--- a/data/sources/countries/guyana.xlsx
+++ b/data/sources/countries/guyana.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +48,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,377 +414,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI71"/>
+  <dimension ref="A1:BE71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="80" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="26" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Id_Investment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Id_Investment_Original</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Id_Seq</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Coordinates</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_ALPHA3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_NUM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Province_ISO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Investor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Area_EN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Area_ES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Detail_ES</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Detail_EN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Joint_Venture</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Origin_Of_Seller</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Project_Type</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>News</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Caso1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Link1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Caso2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Link2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Caso3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Link3</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Caso4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Link4</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Caso5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Link5</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Caso6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Link6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Caso7</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Link7</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Caso8</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Link8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Caso9</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Link9</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Caso10</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Link10</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Caso11</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Link11</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Caso12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Link12</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Caso13</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Link13</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Caso14</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Link14</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>reliability_score</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>reliability_notes</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>cancelled_motivo</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source3</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>source4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>source5</t>
         </is>
       </c>
     </row>
@@ -827,7 +731,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -865,12 +769,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Adquisición completa del proyecto manganese Matthews Ridge de Reunion Gold</t>
+          <t>Adquisición Completa Del Proyecto Manganese Matthews Ridge De Reunion Gold</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Full acquisition from Reunion Gold of the Matthews Ridge manganese project</t>
+          <t>Full Acquisition From Reunion Gold Of The Matthews Ridge Manganese Project</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -879,7 +783,7 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -888,7 +792,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -909,25 +813,20 @@
       <c r="BA2" t="n">
         <v>4</v>
       </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>MONTO CORREGIDO (Allison): estaba en 100. Bosai pago USD 10M a Reunion Gold por el proyecto de manganeso Matthews Ridge en noviembre de 2016. Los USD 400M que circulan son la inversion total proyectada para desarrollar la mina, no el precio de compra.</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
+      <c r="BB2" t="n">
         <v>0</v>
       </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2016/11/05/bosai-buys-matthews-ridge-manganese-project/</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>https://miningconnection.com/surface/news/article/bosai_minerals_to_acquire_reunion_golds_matthews_ridge_manganese_project_fo</t>
+        </is>
+      </c>
       <c r="BE2" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2016/11/05/bosai-buys-matthews-ridge-manganese-project/</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>https://miningconnection.com/surface/news/article/bosai_minerals_to_acquire_reunion_golds_matthews_ridge_manganese_project_fo</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
         <is>
           <t>https://nre.gov.gy/2017/03/21/board-of-directors-of-bosai-minerals-group-meet-with-government-to-update-on-plans-to-advance-new-manganese-project-in-matthews-ridge-region-1/</t>
         </is>
@@ -960,7 +859,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -998,12 +897,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Construcción de banda ancha nacional y de un proyecto "Ciudad Segura"</t>
+          <t>Construcción De Banda Ancha Nacional Y De Un Proyecto "Ciudad Segura"</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Construction of national broadband and 'Safe City' buildout</t>
+          <t>Construction Of National Broadband And 'Safe City' Buildout</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1012,7 +911,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>37.6</v>
+        <v>376</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1021,7 +920,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1042,25 +941,20 @@
       <c r="BA3" t="n">
         <v>3</v>
       </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 376. El contrato del 6 de noviembre de 2017 con el Ministerio de Telecomunicaciones para la Red Nacional de Banda Ancha y el componente Safe City fue de USD 37,6M.</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
+      <c r="BB3" t="n">
         <v>0</v>
       </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>https://www.stabroeknews.com/2019/08/17/opinion/letters/concerned-about-implications-of-huawei-involvement-in-national-broadband-project/</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>https://www.guyanastandard.com/2019/12/07/chinese-company-working-on-guyanas-broadband-project-labelled-as-national-security-threat-by-us-regulators/</t>
+        </is>
+      </c>
       <c r="BE3" t="inlineStr">
-        <is>
-          <t>https://www.stabroeknews.com/2019/08/17/opinion/letters/concerned-about-implications-of-huawei-involvement-in-national-broadband-project/</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>https://www.guyanastandard.com/2019/12/07/chinese-company-working-on-guyanas-broadband-project-labelled-as-national-security-threat-by-us-regulators/</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
         <is>
           <t>https://dpi.gov.gy/national-broadband-network-on-the-horizon/</t>
         </is>
@@ -1093,7 +987,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -1131,12 +1025,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Construcción del puente Demerara River</t>
+          <t>Construcción Del Puente Demerara River</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Construction of Demerara River bridge</t>
+          <t>Construction Of Demerara River Bridge</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1145,7 +1039,7 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>260</v>
+        <v>2600</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1154,7 +1048,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1175,25 +1069,20 @@
       <c r="BA4" t="n">
         <v>4</v>
       </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 2600. El contrato de mayo de 2022 con CRCC por el nuevo puente sobre el rio Demerara fue de USD 260M.</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
+      <c r="BB4" t="n">
         <v>0</v>
       </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2022/05/26/us260m-contract-signed-for-new-demerara-river-bridge/</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>https://www.globalconstructionreview.com/china-railway-wins-260m-contract-to-build-demerara-river-bridge-in-guyana/</t>
+        </is>
+      </c>
       <c r="BE4" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2022/05/26/us260m-contract-signed-for-new-demerara-river-bridge/</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>https://www.globalconstructionreview.com/china-railway-wins-260m-contract-to-build-demerara-river-bridge-in-guyana/</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
         <is>
           <t>https://www.globaltimes.cn/page/202205/1266597.shtml</t>
         </is>
@@ -1226,7 +1115,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -1264,12 +1153,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Construcción del puente Demerara River</t>
+          <t>Construcción Del Puente Demerara River</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Construction of Demerara River bridge</t>
+          <t>Construction Of Demerara River Bridge</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1278,7 +1167,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>260</v>
+        <v>2600</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1287,7 +1176,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1308,25 +1197,20 @@
       <c r="BA5" t="n">
         <v>4</v>
       </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 2600. El contrato de mayo de 2022 con CRCC por el nuevo puente sobre el rio Demerara fue de USD 260M.</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
+      <c r="BB5" t="n">
         <v>0</v>
       </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2022/05/26/us260m-contract-signed-for-new-demerara-river-bridge/</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>https://www.globalconstructionreview.com/china-railway-wins-260m-contract-to-build-demerara-river-bridge-in-guyana/</t>
+        </is>
+      </c>
       <c r="BE5" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2022/05/26/us260m-contract-signed-for-new-demerara-river-bridge/</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>https://www.globalconstructionreview.com/china-railway-wins-260m-contract-to-build-demerara-river-bridge-in-guyana/</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
         <is>
           <t>https://www.globaltimes.cn/page/202205/1266597.shtml</t>
         </is>
@@ -1359,7 +1243,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -1397,12 +1281,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Construcción del puente Demerara River</t>
+          <t>Construcción Del Puente Demerara River</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Construction of Demerara River bridge</t>
+          <t>Construction Of Demerara River Bridge</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1411,7 +1295,7 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>260</v>
+        <v>2600</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1420,7 +1304,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1441,25 +1325,20 @@
       <c r="BA6" t="n">
         <v>4</v>
       </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 2600. El contrato de mayo de 2022 con CRCC por el nuevo puente sobre el rio Demerara fue de USD 260M.</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
+      <c r="BB6" t="n">
         <v>0</v>
       </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2022/05/26/us260m-contract-signed-for-new-demerara-river-bridge/</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>https://www.globalconstructionreview.com/china-railway-wins-260m-contract-to-build-demerara-river-bridge-in-guyana/</t>
+        </is>
+      </c>
       <c r="BE6" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2022/05/26/us260m-contract-signed-for-new-demerara-river-bridge/</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>https://www.globalconstructionreview.com/china-railway-wins-260m-contract-to-build-demerara-river-bridge-in-guyana/</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
         <is>
           <t>https://www.globaltimes.cn/page/202205/1266597.shtml</t>
         </is>
@@ -1492,7 +1371,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -1530,12 +1409,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1544,7 +1423,7 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1553,7 +1432,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1574,25 +1453,20 @@
       <c r="BA7" t="n">
         <v>4</v>
       </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
+      <c r="BB7" t="n">
         <v>0</v>
       </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE7" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -1625,7 +1499,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -1663,12 +1537,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1677,7 +1551,7 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1686,7 +1560,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1707,25 +1581,20 @@
       <c r="BA8" t="n">
         <v>4</v>
       </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
+      <c r="BB8" t="n">
         <v>0</v>
       </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE8" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -1758,7 +1627,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -1796,12 +1665,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1810,7 +1679,7 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1819,7 +1688,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1840,25 +1709,20 @@
       <c r="BA9" t="n">
         <v>4</v>
       </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
+      <c r="BB9" t="n">
         <v>0</v>
       </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE9" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -1891,7 +1755,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -1929,12 +1793,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1943,7 +1807,7 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1952,7 +1816,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1973,25 +1837,20 @@
       <c r="BA10" t="n">
         <v>4</v>
       </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
+      <c r="BB10" t="n">
         <v>0</v>
       </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE10" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -2024,7 +1883,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -2062,12 +1921,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -2076,7 +1935,7 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -2085,7 +1944,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -2106,25 +1965,20 @@
       <c r="BA11" t="n">
         <v>4</v>
       </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
+      <c r="BB11" t="n">
         <v>0</v>
       </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE11" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -2157,7 +2011,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -2195,12 +2049,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2209,7 +2063,7 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -2218,7 +2072,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2239,25 +2093,20 @@
       <c r="BA12" t="n">
         <v>4</v>
       </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
+      <c r="BB12" t="n">
         <v>0</v>
       </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE12" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -2290,7 +2139,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -2328,12 +2177,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2342,7 +2191,7 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -2351,7 +2200,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2372,25 +2221,20 @@
       <c r="BA13" t="n">
         <v>4</v>
       </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
+      <c r="BB13" t="n">
         <v>0</v>
       </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE13" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -2423,7 +2267,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -2461,12 +2305,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2475,7 +2319,7 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2484,7 +2328,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2505,25 +2349,20 @@
       <c r="BA14" t="n">
         <v>4</v>
       </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC14" t="n">
+      <c r="BB14" t="n">
         <v>0</v>
       </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE14" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -2556,7 +2395,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -2594,12 +2433,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2608,7 +2447,7 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2617,7 +2456,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2638,25 +2477,20 @@
       <c r="BA15" t="n">
         <v>4</v>
       </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC15" t="n">
+      <c r="BB15" t="n">
         <v>0</v>
       </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE15" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -2689,7 +2523,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -2727,12 +2561,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2741,7 +2575,7 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2750,7 +2584,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2771,25 +2605,20 @@
       <c r="BA16" t="n">
         <v>4</v>
       </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC16" t="n">
+      <c r="BB16" t="n">
         <v>0</v>
       </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE16" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -2822,7 +2651,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -2860,12 +2689,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2874,7 +2703,7 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2883,7 +2712,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2904,25 +2733,20 @@
       <c r="BA17" t="n">
         <v>4</v>
       </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC17" t="n">
+      <c r="BB17" t="n">
         <v>0</v>
       </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE17" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -2955,7 +2779,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -2993,12 +2817,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -3007,7 +2831,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -3016,7 +2840,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -3037,25 +2861,20 @@
       <c r="BA18" t="n">
         <v>4</v>
       </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC18" t="n">
+      <c r="BB18" t="n">
         <v>0</v>
       </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE18" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -3088,7 +2907,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -3126,12 +2945,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -3140,7 +2959,7 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -3149,7 +2968,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -3170,25 +2989,20 @@
       <c r="BA19" t="n">
         <v>4</v>
       </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC19" t="n">
+      <c r="BB19" t="n">
         <v>0</v>
       </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE19" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -3221,7 +3035,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -3259,12 +3073,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -3273,7 +3087,7 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -3282,7 +3096,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -3303,25 +3117,20 @@
       <c r="BA20" t="n">
         <v>4</v>
       </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
+      <c r="BB20" t="n">
         <v>0</v>
       </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE20" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -3354,7 +3163,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -3392,12 +3201,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3406,7 +3215,7 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -3415,7 +3224,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -3436,25 +3245,20 @@
       <c r="BA21" t="n">
         <v>4</v>
       </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
+      <c r="BB21" t="n">
         <v>0</v>
       </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE21" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -3487,7 +3291,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -3525,12 +3329,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -3539,7 +3343,7 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -3548,7 +3352,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -3569,25 +3373,20 @@
       <c r="BA22" t="n">
         <v>4</v>
       </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC22" t="n">
+      <c r="BB22" t="n">
         <v>0</v>
       </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE22" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -3620,7 +3419,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -3658,12 +3457,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3672,7 +3471,7 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -3681,7 +3480,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -3702,25 +3501,20 @@
       <c r="BA23" t="n">
         <v>4</v>
       </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC23" t="n">
+      <c r="BB23" t="n">
         <v>0</v>
       </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE23" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -3753,7 +3547,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -3791,12 +3585,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3805,7 +3599,7 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -3814,7 +3608,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -3835,25 +3629,20 @@
       <c r="BA24" t="n">
         <v>4</v>
       </c>
-      <c r="BB24" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC24" t="n">
+      <c r="BB24" t="n">
         <v>0</v>
       </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE24" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF24" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG24" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -3886,7 +3675,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -3924,12 +3713,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3938,7 +3727,7 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -3947,7 +3736,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3968,25 +3757,20 @@
       <c r="BA25" t="n">
         <v>4</v>
       </c>
-      <c r="BB25" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC25" t="n">
+      <c r="BB25" t="n">
         <v>0</v>
       </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE25" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF25" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG25" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -4019,7 +3803,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -4057,12 +3841,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -4071,7 +3855,7 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -4080,7 +3864,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -4101,25 +3885,20 @@
       <c r="BA26" t="n">
         <v>4</v>
       </c>
-      <c r="BB26" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC26" t="n">
+      <c r="BB26" t="n">
         <v>0</v>
       </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE26" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF26" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG26" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -4152,7 +3931,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -4190,12 +3969,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -4204,7 +3983,7 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -4213,7 +3992,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -4234,25 +4013,20 @@
       <c r="BA27" t="n">
         <v>4</v>
       </c>
-      <c r="BB27" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC27" t="n">
+      <c r="BB27" t="n">
         <v>0</v>
       </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE27" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF27" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG27" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -4285,7 +4059,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -4323,12 +4097,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4337,7 +4111,7 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -4346,7 +4120,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -4367,25 +4141,20 @@
       <c r="BA28" t="n">
         <v>4</v>
       </c>
-      <c r="BB28" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC28" t="n">
+      <c r="BB28" t="n">
         <v>0</v>
       </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE28" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF28" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG28" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -4418,7 +4187,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -4456,12 +4225,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -4470,7 +4239,7 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -4479,7 +4248,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -4500,25 +4269,20 @@
       <c r="BA29" t="n">
         <v>4</v>
       </c>
-      <c r="BB29" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC29" t="n">
+      <c r="BB29" t="n">
         <v>0</v>
       </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE29" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF29" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -4551,7 +4315,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -4589,12 +4353,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -4603,7 +4367,7 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -4612,7 +4376,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -4633,25 +4397,20 @@
       <c r="BA30" t="n">
         <v>4</v>
       </c>
-      <c r="BB30" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC30" t="n">
+      <c r="BB30" t="n">
         <v>0</v>
       </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE30" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF30" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG30" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -4684,7 +4443,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -4722,12 +4481,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4736,7 +4495,7 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -4745,7 +4504,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -4766,25 +4525,20 @@
       <c r="BA31" t="n">
         <v>4</v>
       </c>
-      <c r="BB31" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC31" t="n">
+      <c r="BB31" t="n">
         <v>0</v>
       </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE31" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF31" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -4817,7 +4571,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -4855,12 +4609,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -4869,7 +4623,7 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -4878,7 +4632,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -4899,25 +4653,20 @@
       <c r="BA32" t="n">
         <v>4</v>
       </c>
-      <c r="BB32" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC32" t="n">
+      <c r="BB32" t="n">
         <v>0</v>
       </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE32" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF32" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG32" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -4950,7 +4699,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -4988,12 +4737,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -5002,7 +4751,7 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -5011,7 +4760,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -5032,25 +4781,20 @@
       <c r="BA33" t="n">
         <v>4</v>
       </c>
-      <c r="BB33" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC33" t="n">
+      <c r="BB33" t="n">
         <v>0</v>
       </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE33" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF33" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -5083,7 +4827,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -5121,12 +4865,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Construcción de la carretera Eccles-Great Diamond</t>
+          <t>Construcción De La Carretera Eccles-Great Diamond</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Construction of Eccles-Great Diamond road</t>
+          <t>Construction Of Eccles-Great Diamond Road</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -5144,7 +4888,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -5165,25 +4909,20 @@
       <c r="BA34" t="n">
         <v>3</v>
       </c>
-      <c r="BB34" t="inlineStr">
-        <is>
-          <t>Allison confirma la corrección: monto estaba en dólares guyaneses, no USD. GYD 1,019M equivale a \~USD 4.9M. China Railway First Group fue uno de 12 contratistas para la autopista Eccles-Diamond de 4 carriles, con presupuesto total de GYD 13,300M (\~USD 63.8M). Tres fuentes guyanesas confirman el proyecto y la participación de empresa china, aunque el lote específico de CRFG no se detalla individualmente.</t>
-        </is>
-      </c>
-      <c r="BC34" t="n">
+      <c r="BB34" t="n">
         <v>0</v>
       </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
+        </is>
+      </c>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
+        </is>
+      </c>
       <c r="BE34" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
-        </is>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
@@ -5216,7 +4955,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -5254,12 +4993,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Construcción de la carretera Eccles-Great Diamond</t>
+          <t>Construcción De La Carretera Eccles-Great Diamond</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Construction of Eccles-Great Diamond road</t>
+          <t>Construction Of Eccles-Great Diamond Road</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -5277,7 +5016,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -5298,25 +5037,20 @@
       <c r="BA35" t="n">
         <v>3</v>
       </c>
-      <c r="BB35" t="inlineStr">
-        <is>
-          <t>Allison confirma la corrección: monto estaba en dólares guyaneses, no USD. GYD 1,019M equivale a \~USD 4.9M. China Railway First Group fue uno de 12 contratistas para la autopista Eccles-Diamond de 4 carriles, con presupuesto total de GYD 13,300M (\~USD 63.8M). Tres fuentes guyanesas confirman el proyecto y la participación de empresa china, aunque el lote específico de CRFG no se detalla individualmente.</t>
-        </is>
-      </c>
-      <c r="BC35" t="n">
+      <c r="BB35" t="n">
         <v>0</v>
       </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
+        </is>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
+        </is>
+      </c>
       <c r="BE35" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
-        </is>
-      </c>
-      <c r="BF35" t="inlineStr">
-        <is>
-          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
-        </is>
-      </c>
-      <c r="BG35" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
@@ -5349,7 +5083,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -5387,12 +5121,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Construcción de la carretera Eccles-Great Diamond</t>
+          <t>Construcción De La Carretera Eccles-Great Diamond</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Construction of Eccles-Great Diamond road</t>
+          <t>Construction Of Eccles-Great Diamond Road</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -5410,7 +5144,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -5431,25 +5165,20 @@
       <c r="BA36" t="n">
         <v>3</v>
       </c>
-      <c r="BB36" t="inlineStr">
-        <is>
-          <t>Allison confirma la corrección: monto estaba en dólares guyaneses, no USD. GYD 1,019M equivale a \~USD 4.9M. China Railway First Group fue uno de 12 contratistas para la autopista Eccles-Diamond de 4 carriles, con presupuesto total de GYD 13,300M (\~USD 63.8M). Tres fuentes guyanesas confirman el proyecto y la participación de empresa china, aunque el lote específico de CRFG no se detalla individualmente.</t>
-        </is>
-      </c>
-      <c r="BC36" t="n">
+      <c r="BB36" t="n">
         <v>0</v>
       </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
+        </is>
+      </c>
       <c r="BE36" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
-        </is>
-      </c>
-      <c r="BF36" t="inlineStr">
-        <is>
-          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
-        </is>
-      </c>
-      <c r="BG36" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
@@ -5482,7 +5211,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -5520,12 +5249,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Construcción de la carretera Eccles-Great Diamond</t>
+          <t>Construcción De La Carretera Eccles-Great Diamond</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Construction of Eccles-Great Diamond road</t>
+          <t>Construction Of Eccles-Great Diamond Road</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -5543,7 +5272,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -5564,25 +5293,20 @@
       <c r="BA37" t="n">
         <v>3</v>
       </c>
-      <c r="BB37" t="inlineStr">
-        <is>
-          <t>Allison confirma la corrección: monto estaba en dólares guyaneses, no USD. GYD 1,019M equivale a \~USD 4.9M. China Railway First Group fue uno de 12 contratistas para la autopista Eccles-Diamond de 4 carriles, con presupuesto total de GYD 13,300M (\~USD 63.8M). Tres fuentes guyanesas confirman el proyecto y la participación de empresa china, aunque el lote específico de CRFG no se detalla individualmente.</t>
-        </is>
-      </c>
-      <c r="BC37" t="n">
+      <c r="BB37" t="n">
         <v>0</v>
       </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
+        </is>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
+        </is>
+      </c>
       <c r="BE37" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
-        </is>
-      </c>
-      <c r="BF37" t="inlineStr">
-        <is>
-          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
-        </is>
-      </c>
-      <c r="BG37" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
@@ -5615,7 +5339,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -5653,12 +5377,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Construcción de la carretera Eccles-Great Diamond</t>
+          <t>Construcción De La Carretera Eccles-Great Diamond</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Construction of Eccles-Great Diamond road</t>
+          <t>Construction Of Eccles-Great Diamond Road</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -5676,7 +5400,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -5697,25 +5421,20 @@
       <c r="BA38" t="n">
         <v>3</v>
       </c>
-      <c r="BB38" t="inlineStr">
-        <is>
-          <t>Allison confirma la corrección: monto estaba en dólares guyaneses, no USD. GYD 1,019M equivale a \~USD 4.9M. China Railway First Group fue uno de 12 contratistas para la autopista Eccles-Diamond de 4 carriles, con presupuesto total de GYD 13,300M (\~USD 63.8M). Tres fuentes guyanesas confirman el proyecto y la participación de empresa china, aunque el lote específico de CRFG no se detalla individualmente.</t>
-        </is>
-      </c>
-      <c r="BC38" t="n">
+      <c r="BB38" t="n">
         <v>0</v>
       </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
+        </is>
+      </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
+        </is>
+      </c>
       <c r="BE38" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
-        </is>
-      </c>
-      <c r="BF38" t="inlineStr">
-        <is>
-          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
-        </is>
-      </c>
-      <c r="BG38" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
@@ -5748,7 +5467,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -5786,12 +5505,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Construcción de la carretera Eccles-Great Diamond</t>
+          <t>Construcción De La Carretera Eccles-Great Diamond</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Construction of Eccles-Great Diamond road</t>
+          <t>Construction Of Eccles-Great Diamond Road</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -5809,7 +5528,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -5830,25 +5549,20 @@
       <c r="BA39" t="n">
         <v>3</v>
       </c>
-      <c r="BB39" t="inlineStr">
-        <is>
-          <t>Allison confirma la corrección: monto estaba en dólares guyaneses, no USD. GYD 1,019M equivale a \~USD 4.9M. China Railway First Group fue uno de 12 contratistas para la autopista Eccles-Diamond de 4 carriles, con presupuesto total de GYD 13,300M (\~USD 63.8M). Tres fuentes guyanesas confirman el proyecto y la participación de empresa china, aunque el lote específico de CRFG no se detalla individualmente.</t>
-        </is>
-      </c>
-      <c r="BC39" t="n">
+      <c r="BB39" t="n">
         <v>0</v>
       </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
+        </is>
+      </c>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
+        </is>
+      </c>
       <c r="BE39" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
-        </is>
-      </c>
-      <c r="BF39" t="inlineStr">
-        <is>
-          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
-        </is>
-      </c>
-      <c r="BG39" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
@@ -5881,7 +5595,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -5919,12 +5633,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Construcción de la carretera Eccles-Great Diamond</t>
+          <t>Construcción De La Carretera Eccles-Great Diamond</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Construction of Eccles-Great Diamond road</t>
+          <t>Construction Of Eccles-Great Diamond Road</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -5942,7 +5656,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
@@ -5963,25 +5677,20 @@
       <c r="BA40" t="n">
         <v>3</v>
       </c>
-      <c r="BB40" t="inlineStr">
-        <is>
-          <t>Allison confirma la corrección: monto estaba en dólares guyaneses, no USD. GYD 1,019M equivale a \~USD 4.9M. China Railway First Group fue uno de 12 contratistas para la autopista Eccles-Diamond de 4 carriles, con presupuesto total de GYD 13,300M (\~USD 63.8M). Tres fuentes guyanesas confirman el proyecto y la participación de empresa china, aunque el lote específico de CRFG no se detalla individualmente.</t>
-        </is>
-      </c>
-      <c r="BC40" t="n">
+      <c r="BB40" t="n">
         <v>0</v>
       </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
+        </is>
+      </c>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
+        </is>
+      </c>
       <c r="BE40" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
-        </is>
-      </c>
-      <c r="BF40" t="inlineStr">
-        <is>
-          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
-        </is>
-      </c>
-      <c r="BG40" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
@@ -6014,7 +5723,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -6052,12 +5761,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Construcción de la carretera Eccles-Great Diamond</t>
+          <t>Construcción De La Carretera Eccles-Great Diamond</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Construction of Eccles-Great Diamond road</t>
+          <t>Construction Of Eccles-Great Diamond Road</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -6075,7 +5784,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -6096,25 +5805,20 @@
       <c r="BA41" t="n">
         <v>3</v>
       </c>
-      <c r="BB41" t="inlineStr">
-        <is>
-          <t>Allison confirma la corrección: monto estaba en dólares guyaneses, no USD. GYD 1,019M equivale a \~USD 4.9M. China Railway First Group fue uno de 12 contratistas para la autopista Eccles-Diamond de 4 carriles, con presupuesto total de GYD 13,300M (\~USD 63.8M). Tres fuentes guyanesas confirman el proyecto y la participación de empresa china, aunque el lote específico de CRFG no se detalla individualmente.</t>
-        </is>
-      </c>
-      <c r="BC41" t="n">
+      <c r="BB41" t="n">
         <v>0</v>
       </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
+        </is>
+      </c>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
+        </is>
+      </c>
       <c r="BE41" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
-        </is>
-      </c>
-      <c r="BF41" t="inlineStr">
-        <is>
-          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
-        </is>
-      </c>
-      <c r="BG41" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
@@ -6147,7 +5851,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -6185,12 +5889,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Construcción de la carretera Eccles-Great Diamond</t>
+          <t>Construcción De La Carretera Eccles-Great Diamond</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Construction of Eccles-Great Diamond road</t>
+          <t>Construction Of Eccles-Great Diamond Road</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -6208,7 +5912,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -6229,25 +5933,20 @@
       <c r="BA42" t="n">
         <v>3</v>
       </c>
-      <c r="BB42" t="inlineStr">
-        <is>
-          <t>Allison confirma la corrección: monto estaba en dólares guyaneses, no USD. GYD 1,019M equivale a \~USD 4.9M. China Railway First Group fue uno de 12 contratistas para la autopista Eccles-Diamond de 4 carriles, con presupuesto total de GYD 13,300M (\~USD 63.8M). Tres fuentes guyanesas confirman el proyecto y la participación de empresa china, aunque el lote específico de CRFG no se detalla individualmente.</t>
-        </is>
-      </c>
-      <c r="BC42" t="n">
+      <c r="BB42" t="n">
         <v>0</v>
       </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
+        </is>
+      </c>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
+        </is>
+      </c>
       <c r="BE42" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
-        </is>
-      </c>
-      <c r="BF42" t="inlineStr">
-        <is>
-          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
-        </is>
-      </c>
-      <c r="BG42" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
@@ -6280,7 +5979,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -6318,12 +6017,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Construcción de la carretera Eccles-Great Diamond</t>
+          <t>Construcción De La Carretera Eccles-Great Diamond</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Construction of Eccles-Great Diamond road</t>
+          <t>Construction Of Eccles-Great Diamond Road</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -6341,7 +6040,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -6362,25 +6061,20 @@
       <c r="BA43" t="n">
         <v>3</v>
       </c>
-      <c r="BB43" t="inlineStr">
-        <is>
-          <t>Allison confirma la corrección: monto estaba en dólares guyaneses, no USD. GYD 1,019M equivale a \~USD 4.9M. China Railway First Group fue uno de 12 contratistas para la autopista Eccles-Diamond de 4 carriles, con presupuesto total de GYD 13,300M (\~USD 63.8M). Tres fuentes guyanesas confirman el proyecto y la participación de empresa china, aunque el lote específico de CRFG no se detalla individualmente.</t>
-        </is>
-      </c>
-      <c r="BC43" t="n">
+      <c r="BB43" t="n">
         <v>0</v>
       </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
+        </is>
+      </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
+        </is>
+      </c>
       <c r="BE43" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
-        </is>
-      </c>
-      <c r="BF43" t="inlineStr">
-        <is>
-          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
-        </is>
-      </c>
-      <c r="BG43" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
@@ -6413,7 +6107,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -6451,12 +6145,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Construcción de la carretera Eccles-Great Diamond</t>
+          <t>Construcción De La Carretera Eccles-Great Diamond</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Construction of Eccles-Great Diamond road</t>
+          <t>Construction Of Eccles-Great Diamond Road</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -6474,7 +6168,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -6495,25 +6189,20 @@
       <c r="BA44" t="n">
         <v>3</v>
       </c>
-      <c r="BB44" t="inlineStr">
-        <is>
-          <t>Allison confirma la corrección: monto estaba en dólares guyaneses, no USD. GYD 1,019M equivale a \~USD 4.9M. China Railway First Group fue uno de 12 contratistas para la autopista Eccles-Diamond de 4 carriles, con presupuesto total de GYD 13,300M (\~USD 63.8M). Tres fuentes guyanesas confirman el proyecto y la participación de empresa china, aunque el lote específico de CRFG no se detalla individualmente.</t>
-        </is>
-      </c>
-      <c r="BC44" t="n">
+      <c r="BB44" t="n">
         <v>0</v>
       </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
+        </is>
+      </c>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
+        </is>
+      </c>
       <c r="BE44" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
-        </is>
-      </c>
-      <c r="BF44" t="inlineStr">
-        <is>
-          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
-        </is>
-      </c>
-      <c r="BG44" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
@@ -6546,7 +6235,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -6584,12 +6273,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Construcción de la carretera Eccles-Great Diamond</t>
+          <t>Construcción De La Carretera Eccles-Great Diamond</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Construction of Eccles-Great Diamond road</t>
+          <t>Construction Of Eccles-Great Diamond Road</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -6607,7 +6296,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -6628,25 +6317,20 @@
       <c r="BA45" t="n">
         <v>3</v>
       </c>
-      <c r="BB45" t="inlineStr">
-        <is>
-          <t>Allison confirma la corrección: monto estaba en dólares guyaneses, no USD. GYD 1,019M equivale a \~USD 4.9M. China Railway First Group fue uno de 12 contratistas para la autopista Eccles-Diamond de 4 carriles, con presupuesto total de GYD 13,300M (\~USD 63.8M). Tres fuentes guyanesas confirman el proyecto y la participación de empresa china, aunque el lote específico de CRFG no se detalla individualmente.</t>
-        </is>
-      </c>
-      <c r="BC45" t="n">
+      <c r="BB45" t="n">
         <v>0</v>
       </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
+        </is>
+      </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
+        </is>
+      </c>
       <c r="BE45" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
-        </is>
-      </c>
-      <c r="BF45" t="inlineStr">
-        <is>
-          <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
-        </is>
-      </c>
-      <c r="BG45" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
@@ -6679,7 +6363,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -6717,12 +6401,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Construcción de plantas de tratamiento de agua en Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara and Sheet Anchor, East Canje, and Berbice</t>
+          <t>Construcción De Plantas De Tratamiento De Agua En Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor, East Canje, And Berbice</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Construction of water treatment plants at Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara and Sheet Anchor, East Canje, and Berbice</t>
+          <t>Construction Of Water Treatment Plants At Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor, East Canje, And Berbice</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -6731,7 +6415,7 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>30</v>
+        <v>3977</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -6761,25 +6445,20 @@
       <c r="BA46" t="n">
         <v>3</v>
       </c>
-      <c r="BB46" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 3977. PowerChina firmo en 2017 los contratos de las plantas de tratamiento de agua de Uitvlugt, Diamond y Sheet Anchor/Berbice; el proyecto completo costo unos USD 30M. El desvio era de mas de 100 veces, posiblemente por confusion con dolares guyaneses.</t>
-        </is>
-      </c>
-      <c r="BC46" t="n">
+      <c r="BB46" t="n">
         <v>0</v>
       </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>https://guyanatimesgy.com/contract-inked-with-chinese-firm-for-water-treatment-plants/</t>
+        </is>
+      </c>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>https://en.powerchina.cn/2020-02/25/c_714175.htm</t>
+        </is>
+      </c>
       <c r="BE46" t="inlineStr">
-        <is>
-          <t>https://guyanatimesgy.com/contract-inked-with-chinese-firm-for-water-treatment-plants/</t>
-        </is>
-      </c>
-      <c r="BF46" t="inlineStr">
-        <is>
-          <t>https://en.powerchina.cn/2020-02/25/c_714175.htm</t>
-        </is>
-      </c>
-      <c r="BG46" t="inlineStr">
         <is>
           <t>https://www.stabroeknews.com/2017/09/01/news/guyana/chinese-company-to-construct-three-water-plants/</t>
         </is>
@@ -6812,7 +6491,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -6850,12 +6529,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Construcción de plantas de tratamiento de agua en Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara and Sheet Anchor, East Canje, and Berbice</t>
+          <t>Construcción De Plantas De Tratamiento De Agua En Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor, East Canje, And Berbice</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Construction of water treatment plants at Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara and Sheet Anchor, East Canje, and Berbice</t>
+          <t>Construction Of Water Treatment Plants At Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor, East Canje, And Berbice</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -6864,7 +6543,7 @@
         </is>
       </c>
       <c r="R47" t="n">
-        <v>30</v>
+        <v>3977</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -6894,25 +6573,20 @@
       <c r="BA47" t="n">
         <v>3</v>
       </c>
-      <c r="BB47" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 3977. PowerChina firmo en 2017 los contratos de las plantas de tratamiento de agua de Uitvlugt, Diamond y Sheet Anchor/Berbice; el proyecto completo costo unos USD 30M. El desvio era de mas de 100 veces, posiblemente por confusion con dolares guyaneses.</t>
-        </is>
-      </c>
-      <c r="BC47" t="n">
+      <c r="BB47" t="n">
         <v>0</v>
       </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>https://guyanatimesgy.com/contract-inked-with-chinese-firm-for-water-treatment-plants/</t>
+        </is>
+      </c>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>https://en.powerchina.cn/2020-02/25/c_714175.htm</t>
+        </is>
+      </c>
       <c r="BE47" t="inlineStr">
-        <is>
-          <t>https://guyanatimesgy.com/contract-inked-with-chinese-firm-for-water-treatment-plants/</t>
-        </is>
-      </c>
-      <c r="BF47" t="inlineStr">
-        <is>
-          <t>https://en.powerchina.cn/2020-02/25/c_714175.htm</t>
-        </is>
-      </c>
-      <c r="BG47" t="inlineStr">
         <is>
           <t>https://www.stabroeknews.com/2017/09/01/news/guyana/chinese-company-to-construct-three-water-plants/</t>
         </is>
@@ -6945,7 +6619,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -6983,12 +6657,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Construcción de plantas de tratamiento de agua en Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara and Sheet Anchor, East Canje, and Berbice</t>
+          <t>Construcción De Plantas De Tratamiento De Agua En Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor, East Canje, And Berbice</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Construction of water treatment plants at Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara and Sheet Anchor, East Canje, and Berbice</t>
+          <t>Construction Of Water Treatment Plants At Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor, East Canje, And Berbice</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -6997,7 +6671,7 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>30</v>
+        <v>3977</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -7027,25 +6701,20 @@
       <c r="BA48" t="n">
         <v>3</v>
       </c>
-      <c r="BB48" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 3977. PowerChina firmo en 2017 los contratos de las plantas de tratamiento de agua de Uitvlugt, Diamond y Sheet Anchor/Berbice; el proyecto completo costo unos USD 30M. El desvio era de mas de 100 veces, posiblemente por confusion con dolares guyaneses.</t>
-        </is>
-      </c>
-      <c r="BC48" t="n">
+      <c r="BB48" t="n">
         <v>0</v>
       </c>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>https://guyanatimesgy.com/contract-inked-with-chinese-firm-for-water-treatment-plants/</t>
+        </is>
+      </c>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>https://en.powerchina.cn/2020-02/25/c_714175.htm</t>
+        </is>
+      </c>
       <c r="BE48" t="inlineStr">
-        <is>
-          <t>https://guyanatimesgy.com/contract-inked-with-chinese-firm-for-water-treatment-plants/</t>
-        </is>
-      </c>
-      <c r="BF48" t="inlineStr">
-        <is>
-          <t>https://en.powerchina.cn/2020-02/25/c_714175.htm</t>
-        </is>
-      </c>
-      <c r="BG48" t="inlineStr">
         <is>
           <t>https://www.stabroeknews.com/2017/09/01/news/guyana/chinese-company-to-construct-three-water-plants/</t>
         </is>
@@ -7078,7 +6747,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -7116,12 +6785,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Construcción de seis hospitales regionales</t>
+          <t>Construcción De Seis Hospitales Regionales</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Construction of six regional hospitals</t>
+          <t>Construction Of Six Regional Hospitals</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -7160,20 +6829,20 @@
       <c r="BA49" t="n">
         <v>3</v>
       </c>
-      <c r="BC49" t="n">
+      <c r="BB49" t="n">
         <v>0</v>
       </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
+        </is>
+      </c>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
+        </is>
+      </c>
       <c r="BE49" t="inlineStr">
-        <is>
-          <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
-        </is>
-      </c>
-      <c r="BF49" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
-        </is>
-      </c>
-      <c r="BG49" t="inlineStr">
         <is>
           <t>https://www.sinomach.com.cn/en/MediaCenter/News/202509/t20250919_580641.html</t>
         </is>
@@ -7206,7 +6875,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -7244,12 +6913,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Construcción de seis hospitales regionales</t>
+          <t>Construcción De Seis Hospitales Regionales</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Construction of six regional hospitals</t>
+          <t>Construction Of Six Regional Hospitals</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -7288,20 +6957,20 @@
       <c r="BA50" t="n">
         <v>3</v>
       </c>
-      <c r="BC50" t="n">
+      <c r="BB50" t="n">
         <v>0</v>
       </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
+        </is>
+      </c>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
+        </is>
+      </c>
       <c r="BE50" t="inlineStr">
-        <is>
-          <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
-        </is>
-      </c>
-      <c r="BF50" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
-        </is>
-      </c>
-      <c r="BG50" t="inlineStr">
         <is>
           <t>https://www.sinomach.com.cn/en/MediaCenter/News/202509/t20250919_580641.html</t>
         </is>
@@ -7334,7 +7003,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -7372,12 +7041,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Construcción de seis hospitales regionales</t>
+          <t>Construcción De Seis Hospitales Regionales</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Construction of six regional hospitals</t>
+          <t>Construction Of Six Regional Hospitals</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -7416,20 +7085,20 @@
       <c r="BA51" t="n">
         <v>3</v>
       </c>
-      <c r="BC51" t="n">
+      <c r="BB51" t="n">
         <v>0</v>
       </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
+        </is>
+      </c>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
+        </is>
+      </c>
       <c r="BE51" t="inlineStr">
-        <is>
-          <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
-        </is>
-      </c>
-      <c r="BF51" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
-        </is>
-      </c>
-      <c r="BG51" t="inlineStr">
         <is>
           <t>https://www.sinomach.com.cn/en/MediaCenter/News/202509/t20250919_580641.html</t>
         </is>
@@ -7462,7 +7131,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -7500,12 +7169,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Construcción de seis hospitales regionales</t>
+          <t>Construcción De Seis Hospitales Regionales</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Construction of six regional hospitals</t>
+          <t>Construction Of Six Regional Hospitals</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -7544,20 +7213,20 @@
       <c r="BA52" t="n">
         <v>3</v>
       </c>
-      <c r="BC52" t="n">
+      <c r="BB52" t="n">
         <v>0</v>
       </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
+        </is>
+      </c>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
+        </is>
+      </c>
       <c r="BE52" t="inlineStr">
-        <is>
-          <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
-        </is>
-      </c>
-      <c r="BF52" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
-        </is>
-      </c>
-      <c r="BG52" t="inlineStr">
         <is>
           <t>https://www.sinomach.com.cn/en/MediaCenter/News/202509/t20250919_580641.html</t>
         </is>
@@ -7590,7 +7259,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -7628,12 +7297,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Construcción de seis hospitales regionales</t>
+          <t>Construcción De Seis Hospitales Regionales</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Construction of six regional hospitals</t>
+          <t>Construction Of Six Regional Hospitals</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -7672,20 +7341,20 @@
       <c r="BA53" t="n">
         <v>3</v>
       </c>
-      <c r="BC53" t="n">
+      <c r="BB53" t="n">
         <v>0</v>
       </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
+        </is>
+      </c>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
+        </is>
+      </c>
       <c r="BE53" t="inlineStr">
-        <is>
-          <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
-        </is>
-      </c>
-      <c r="BF53" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
-        </is>
-      </c>
-      <c r="BG53" t="inlineStr">
         <is>
           <t>https://www.sinomach.com.cn/en/MediaCenter/News/202509/t20250919_580641.html</t>
         </is>
@@ -7718,7 +7387,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -7756,12 +7425,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Construcción del King's Hotel</t>
+          <t>Construcción Del King'S Hotel</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Construction of King's Hotel</t>
+          <t>Construction Of King'S Hotel</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -7779,7 +7448,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -7800,15 +7469,10 @@
       <c r="BA54" t="n">
         <v>0</v>
       </c>
-      <c r="BC54" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD54" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE54" t="inlineStr">
+      <c r="BB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC54" t="inlineStr">
         <is>
           <t>https://guyanachronicle.com/2020/11/25/450570/</t>
         </is>
@@ -7841,7 +7505,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -7879,12 +7543,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Construcción del aeropuerto internacional Cheddi Jagan</t>
+          <t>Construcción Del Aeropuerto Internacional Cheddi Jagan</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Construction of Cheddi Jagan International Airport</t>
+          <t>Construction Of Cheddi Jagan International Airport</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -7893,7 +7557,7 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>138</v>
+        <v>1380</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -7948,40 +7612,25 @@
       <c r="AF55" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36574/</t>
-        </is>
-      </c>
-      <c r="AG55" t="inlineStr">
-        <is>
-          <t>Zeng Peng. (2024). “海外中小型航站楼改造探究——以圭亚那切迪贾根国际机场改造为例,” 广东土木与建筑, 2020.</t>
-        </is>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>https://oversea.cnki.net/KCMS/detail/detail.aspx?dbcode=CJFD\&amp;dbname=CJFDLAST2020\&amp;filename=GDTM202005008\&amp;uniplatform=OVERSEA\&amp;v=OJVEcgBQhQJmGVCjpiuiXgBL\_QgzPkjpLANfc4OlJlBkOEKKvHLqVF9lwtPJqMWx</t>
         </is>
       </c>
       <c r="BA55" t="n">
         <v>4</v>
       </c>
-      <c r="BB55" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1380. El contrato de noviembre de 2011 para ampliar el aeropuerto Cheddi Jagan fue de USD 138M, confirmado por AidData, Caribbean Journal y Airport Technology.</t>
-        </is>
-      </c>
-      <c r="BC55" t="n">
+      <c r="BB55" t="n">
         <v>0</v>
       </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>https://www.caribjournal.com/2011/11/19/guyanas-cabinet-approves-138-million-airport-expansion-deal-with-china/</t>
+        </is>
+      </c>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>https://www.airport-technology.com/projects/cheddi-jagan-international-airport-expansion-guyana/</t>
+        </is>
+      </c>
       <c r="BE55" t="inlineStr">
-        <is>
-          <t>https://www.caribjournal.com/2011/11/19/guyanas-cabinet-approves-138-million-airport-expansion-deal-with-china/</t>
-        </is>
-      </c>
-      <c r="BF55" t="inlineStr">
-        <is>
-          <t>https://www.airport-technology.com/projects/cheddi-jagan-international-airport-expansion-guyana/</t>
-        </is>
-      </c>
-      <c r="BG55" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36574/</t>
         </is>
@@ -8014,7 +7663,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -8052,12 +7701,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Adquisición de participación minoritaria en el bloque Stabroek en joint venture con Exxon y Hess</t>
+          <t>Adquisición De Participación Minoritaria En El Bloque Stabroek En Joint Venture Con Exxon Y Hess</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Acquisition of minority stake in the Stabroek block in joint venture with Exxon and Hess</t>
+          <t>Acquisition Of Minority Stake In The Stabroek Block In Joint Venture With Exxon And Hess</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -8103,16 +7752,6 @@
           <t>https://archives.datapages.com/data/specpubs/memoir125/data/433_aapg-sp2150433.htm</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Jule Lümmen. (2024). “Neocolonialism Facilitated by the World Bank? A Case Study of the World Bank’s Involvement in the Development of Guyana’s Oil and Gas Sector,” Global Partnerships and Neocolonialism, 2025.</t>
-        </is>
-      </c>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>https://link.springer.com/chapter/10.1007/978-3-031-87005-7\_5</t>
-        </is>
-      </c>
       <c r="AE56" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. ft.com.</t>
@@ -8121,35 +7760,20 @@
       <c r="AF56" t="inlineStr">
         <is>
           <t>https://www.ft.com/content/3ad64602-88cc-4d4c-ad5e-20993b929bc3</t>
-        </is>
-      </c>
-      <c r="AG56" t="inlineStr">
-        <is>
-          <t>Linda M. Price et al. (2024). “Liza Field, Guyana: The Finding of a Stratigraphic Giant, from Early Exploration to Production,” Memoir 125: Giant Fields of the Decade: 2010–2020, 2021.</t>
-        </is>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>https://archives.datapages.com/data/specpubs/memoir125/data/433\_aapg-sp2150433.htm</t>
         </is>
       </c>
       <c r="BA56" t="n">
         <v>3</v>
       </c>
-      <c r="BB56" t="inlineStr">
-        <is>
-          <t>Confirmado que CNOOC adquirió 25% del bloque Stabroek en 2014 a través de su subsidiaria Nexen (adquirida de Canadá en 2013). La entrada registra '10\*' como monto (inversión nominal o no cuantificada), lo cual es coherente con que la participación fue heredada de la compra de Nexen y no una transacción separada directa en Guyana. La operación está bien documentada aunque el monto específico no es claro.</t>
-        </is>
-      </c>
-      <c r="BC56" t="n">
+      <c r="BB56" t="n">
         <v>0</v>
       </c>
-      <c r="BE56" t="inlineStr">
+      <c r="BC56" t="inlineStr">
         <is>
           <t>https://budsoffshoreenergy.com/2024/03/25/how-china-became-a-factor-in-the-stabroek-guyana-dispute/</t>
         </is>
       </c>
-      <c r="BF56" t="inlineStr">
+      <c r="BD56" t="inlineStr">
         <is>
           <t>https://www.velaw.com/insights/the-stabroek-joa-arbitration-is-it-time-to-revisit-joa-change-in-control-provisions/</t>
         </is>
@@ -8182,7 +7806,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -8220,12 +7844,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -8234,7 +7858,7 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -8243,46 +7867,31 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>Kaieteur News. (2022, October 15). Chinese company awarded US$184M contract for East Coast road project.</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
       <c r="BA57" t="n">
         <v>4</v>
       </c>
-      <c r="BB57" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC57" t="n">
+      <c r="BB57" t="n">
         <v>0</v>
       </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE57" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF57" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG57" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -8315,7 +7924,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -8353,12 +7962,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -8367,7 +7976,7 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -8376,46 +7985,31 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>Kaieteur News. (2022, October 15). Chinese company awarded US$184M contract for East Coast road project.</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
       <c r="BA58" t="n">
         <v>4</v>
       </c>
-      <c r="BB58" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC58" t="n">
+      <c r="BB58" t="n">
         <v>0</v>
       </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE58" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF58" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG58" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -8448,7 +8042,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G59" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -8486,12 +8080,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -8500,7 +8094,7 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -8509,46 +8103,31 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>Kaieteur News. (2022, October 15). Chinese company awarded US$184M contract for East Coast road project.</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
       <c r="BA59" t="n">
         <v>4</v>
       </c>
-      <c r="BB59" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC59" t="n">
+      <c r="BB59" t="n">
         <v>0</v>
       </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE59" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF59" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG59" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -8581,7 +8160,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -8619,12 +8198,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -8633,7 +8212,7 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -8642,46 +8221,31 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Kaieteur News. (2022, October 15). Chinese company awarded US$184M contract for East Coast road project.</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
       <c r="BA60" t="n">
         <v>4</v>
       </c>
-      <c r="BB60" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC60" t="n">
+      <c r="BB60" t="n">
         <v>0</v>
       </c>
+      <c r="BC60" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE60" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF60" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG60" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -8714,7 +8278,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -8752,12 +8316,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Construcción del una carretera de Sheriff Street a Mahaica</t>
+          <t>Construcción Del Una Carretera De Sheriff Street A Mahaica</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Construction of highway from Sheriff Street to Mahaica</t>
+          <t>Construction Of Highway From Sheriff Street To Mahaica</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -8766,7 +8330,7 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>184</v>
+        <v>1840</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -8775,46 +8339,31 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>Kaieteur News. (2022, October 15). Chinese company awarded US$184M contract for East Coast road project.</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
       <c r="BA61" t="n">
         <v>4</v>
       </c>
-      <c r="BB61" t="inlineStr">
-        <is>
-          <t>ERROR DE ESCALA CORREGIDO (Allison): estaba en 1840. El contrato de octubre de 2022 a China Railway First Group por la autopista Sheriff Street-Mahaica fue de USD 184M, confirmado por tres fuentes guyanesas.</t>
-        </is>
-      </c>
-      <c r="BC61" t="n">
+      <c r="BB61" t="n">
         <v>0</v>
       </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
+        </is>
+      </c>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
+        </is>
+      </c>
       <c r="BE61" t="inlineStr">
-        <is>
-          <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
-        </is>
-      </c>
-      <c r="BF61" t="inlineStr">
-        <is>
-          <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
-        </is>
-      </c>
-      <c r="BG61" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
@@ -8847,7 +8396,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G62" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -8885,12 +8434,12 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Adqusición completa del la mina Aurora de Guyana Goldfields</t>
+          <t>Adqusición Completa Del La Mina Aurora De Guyana Goldfields</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Full aquisition from Guyana Goldfields of Aurora mine</t>
+          <t>Full Aquisition From Guyana Goldfields Of Aurora Mine</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -8919,20 +8468,20 @@
       <c r="BA62" t="n">
         <v>5</v>
       </c>
-      <c r="BC62" t="n">
+      <c r="BB62" t="n">
         <v>0</v>
       </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>https://www.mining-technology.com/news/zijin-mining-acquire-guyana-goldfields/</t>
+        </is>
+      </c>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>https://www.zijinmining.com/news/news-detail-119059.htm</t>
+        </is>
+      </c>
       <c r="BE62" t="inlineStr">
-        <is>
-          <t>https://www.mining-technology.com/news/zijin-mining-acquire-guyana-goldfields/</t>
-        </is>
-      </c>
-      <c r="BF62" t="inlineStr">
-        <is>
-          <t>https://www.zijinmining.com/news/news-detail-119059.htm</t>
-        </is>
-      </c>
-      <c r="BG62" t="inlineStr">
         <is>
           <t>https://guyanachronicle.com/2020/06/12/chinese-firm-zijin-mining-acquires-guyana-goldfields-in-cdn323m-deal/</t>
         </is>
@@ -8965,7 +8514,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G63" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -9037,20 +8586,20 @@
       <c r="BA63" t="n">
         <v>3</v>
       </c>
-      <c r="BC63" t="n">
+      <c r="BB63" t="n">
         <v>0</v>
       </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>https://www.stabroeknews.com/2022/04/28/news/guyana/shell-mohamed-signs-us25m-pact-with-chec-for-quarry/</t>
+        </is>
+      </c>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>https://inewsguyana.com/hadis-world-chec-partner-to-supply-1-million-tonnes-of-aggregates-yearly/</t>
+        </is>
+      </c>
       <c r="BE63" t="inlineStr">
-        <is>
-          <t>https://www.stabroeknews.com/2022/04/28/news/guyana/shell-mohamed-signs-us25m-pact-with-chec-for-quarry/</t>
-        </is>
-      </c>
-      <c r="BF63" t="inlineStr">
-        <is>
-          <t>https://inewsguyana.com/hadis-world-chec-partner-to-supply-1-million-tonnes-of-aggregates-yearly/</t>
-        </is>
-      </c>
-      <c r="BG63" t="inlineStr">
         <is>
           <t>https://inewsguyana.com/mohameds-enterprise-partners-with-chinese-firm-for-us25m-quarry-project/</t>
         </is>
@@ -9083,7 +8632,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G64" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -9155,20 +8704,20 @@
       <c r="BA64" t="n">
         <v>3</v>
       </c>
-      <c r="BC64" t="n">
+      <c r="BB64" t="n">
         <v>0</v>
       </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>https://www.stabroeknews.com/2022/04/28/news/guyana/shell-mohamed-signs-us25m-pact-with-chec-for-quarry/</t>
+        </is>
+      </c>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>https://inewsguyana.com/hadis-world-chec-partner-to-supply-1-million-tonnes-of-aggregates-yearly/</t>
+        </is>
+      </c>
       <c r="BE64" t="inlineStr">
-        <is>
-          <t>https://www.stabroeknews.com/2022/04/28/news/guyana/shell-mohamed-signs-us25m-pact-with-chec-for-quarry/</t>
-        </is>
-      </c>
-      <c r="BF64" t="inlineStr">
-        <is>
-          <t>https://inewsguyana.com/hadis-world-chec-partner-to-supply-1-million-tonnes-of-aggregates-yearly/</t>
-        </is>
-      </c>
-      <c r="BG64" t="inlineStr">
         <is>
           <t>https://inewsguyana.com/mohameds-enterprise-partners-with-chinese-firm-for-us25m-quarry-project/</t>
         </is>
@@ -9201,7 +8750,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -9273,20 +8822,20 @@
       <c r="BA65" t="n">
         <v>3</v>
       </c>
-      <c r="BC65" t="n">
+      <c r="BB65" t="n">
         <v>0</v>
       </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>https://www.stabroeknews.com/2022/04/28/news/guyana/shell-mohamed-signs-us25m-pact-with-chec-for-quarry/</t>
+        </is>
+      </c>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>https://inewsguyana.com/hadis-world-chec-partner-to-supply-1-million-tonnes-of-aggregates-yearly/</t>
+        </is>
+      </c>
       <c r="BE65" t="inlineStr">
-        <is>
-          <t>https://www.stabroeknews.com/2022/04/28/news/guyana/shell-mohamed-signs-us25m-pact-with-chec-for-quarry/</t>
-        </is>
-      </c>
-      <c r="BF65" t="inlineStr">
-        <is>
-          <t>https://inewsguyana.com/hadis-world-chec-partner-to-supply-1-million-tonnes-of-aggregates-yearly/</t>
-        </is>
-      </c>
-      <c r="BG65" t="inlineStr">
         <is>
           <t>https://inewsguyana.com/mohameds-enterprise-partners-with-chinese-firm-for-us25m-quarry-project/</t>
         </is>
@@ -9319,7 +8868,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -9357,12 +8906,12 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Construccion of la fábrica de azucar Skeldon</t>
+          <t>Construccion Of La Fábrica De Azucar Skeldon</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Construction of Skeldon Sugar Factory</t>
+          <t>Construction Of Skeldon Sugar Factory</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -9380,14 +8929,14 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="Y66" t="inlineStr">
         <is>
           <t>Ye Jian-qiao. (2024). “圭亚那斯凯尔顿现代化糖厂项目工期索赔的案例探析,” 广西糖业, 2022.</t>
@@ -9396,16 +8945,6 @@
       <c r="Z66" t="inlineStr">
         <is>
           <t>https://www.cnki.net/KCMS/detail/detail.aspx?dbcode=CJFD&amp;dbname=CJFDLAST2022&amp;filename=GXZT202203011&amp;uniplatform=OVERSEA&amp;v=hlu0ySpMhIW51We_35WIk-spUerUyXhlOZvj2Y8FWjU_C6xneEukFSQAf31madmo</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>Ye Jian-qiao. (2024). “圭亚那斯凯尔顿现代化糖厂项目工期索赔的案例探析,” 广西糖业, 2022.</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>https://www.cnki.net/KCMS/detail/detail.aspx?dbcode=CJFD\&amp;dbname=CJFDLAST2022\&amp;filename=GXZT202203011\&amp;uniplatform=OVERSEA\&amp;v=hlu0ySpMhIW51We\_35WIk-spUerUyXhlOZvj2Y8FWjU\_C6xneEukFSQAf31madmo</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
@@ -9421,25 +8960,20 @@
       <c r="BA66" t="n">
         <v>4</v>
       </c>
-      <c r="BB66" t="inlineStr">
-        <is>
-          <t>Bien documentado: CNTIC Trading firmó contrato comercial el 22 de junio de 2004 con GuySuCo para el Proyecto de Modernización Azucarera de Skeldon. El costo final fue \~USD 187-200M, no USD 49M. El monto de USD 49M podría corresponder al préstamo concesional del EXIM Bank de China (RMB 270M = \~USD 40-49M), no al costo total. Proyecto terminado en 2009, confirmado por AidData y GuySuCo.</t>
-        </is>
-      </c>
-      <c r="BC66" t="n">
+      <c r="BB66" t="n">
         <v>0</v>
       </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>https://china.aiddata.org/projects/55943/</t>
+        </is>
+      </c>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>https://guysuco.gy/index.php?option=com_k2&amp;view=item&amp;id=9:skeldon-sugar-modernisation-project-ssmp&amp;Itemid=277&amp;lang=en</t>
+        </is>
+      </c>
       <c r="BE66" t="inlineStr">
-        <is>
-          <t>https://china.aiddata.org/projects/55943/</t>
-        </is>
-      </c>
-      <c r="BF66" t="inlineStr">
-        <is>
-          <t>https://guysuco.gy/index.php?option=com_k2&amp;view=item&amp;id=9:skeldon-sugar-modernisation-project-ssmp&amp;Itemid=277&amp;lang=en</t>
-        </is>
-      </c>
-      <c r="BG66" t="inlineStr">
         <is>
           <t>https://www.stabroeknews.com/2023/11/18/opinion/editorial/revisionism-and-the-skeldon-sugar-factory/</t>
         </is>
@@ -9472,7 +9006,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -9510,12 +9044,12 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Construcción de la sede central de la policía</t>
+          <t>Construcción De La Sede Central De La Policía</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Construction of police headquarters</t>
+          <t>Construction Of Police Headquarters</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -9544,20 +9078,15 @@
       <c r="BA67" t="n">
         <v>3</v>
       </c>
-      <c r="BB67" t="inlineStr">
-        <is>
-          <t>Fuentes confirman que CNQC (Qing Jian Group) participa en la construccion del nuevo cuartel general de la Policia de Guyana (Brickdam Police Station) por USD 28M, junto con R. Bassoo and Sons. La obra inicio en enero de 2024; la entrada registra el ano como 2025, pero el inicio del proyecto fue en 2024.</t>
-        </is>
-      </c>
-      <c r="BC67" t="n">
+      <c r="BB67" t="n">
         <v>0</v>
       </c>
-      <c r="BE67" t="inlineStr">
+      <c r="BC67" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2024/01/09/sod-turned-for-us28m-brickdam-police-station/</t>
         </is>
       </c>
-      <c r="BF67" t="inlineStr">
+      <c r="BD67" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2025/09/18/us28m-brickdam-police-station-on-track-for-june-2026-deadline/</t>
         </is>
@@ -9590,7 +9119,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G68" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -9628,12 +9157,12 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Adqusición de participación mayoritaria en la mina Omai de bauxita</t>
+          <t>Adqusición De Participación Mayoritaria En La Mina Omai De Bauxita</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Acquisition of majority stake in Omai bauxite mine</t>
+          <t>Acquisition Of Majority Stake In Omai Bauxite Mine</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -9679,38 +9208,23 @@
           <t>http://ogneupor-spb.ru/besplatno/2.pdf</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Randolph A. Williams. (2024). “Extractivism and labour in Guyana,” Extractivism and Labour in the Caribbean, 2023.</t>
-        </is>
-      </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>https://d1wqtxts1xzle7.cloudfront.net/83078518/ECD4-5-libre.pdf?1648900517=\&amp;response-content-disposition=inline%3B+filename%3DEl\_capitalismo\_extractivo\_el\_caso\_de\_Guy.pdf\&amp;Expires=1761017007\&amp;Signature=DVSlIXkpE8hOCh1AY3yn1RI\~tr7RGfunLgYU\~aRuhpC3k41kBs9OTOtH2ldEtzfAwYMLW9Dib6GMLxlNCp36R6CzorNe0e6eDgLXqkdztjrYwEW5axz0zwZDuvoXobbj1B3Grlz7FD5Q7nPG5lufcS9hMaXSgqbGXtk9eTn3dugGEke5EgcJY5fFR02v-UzaSS0N1csS1\~LEXjIg7OO5tQcFXKlf7gMPYdxk3FiLUqhaTmYV7qNpQ6h8NZ9kC1P23oXG8-n6hLHEyOGdWeodvkFKTlT-rxYlA-HbFZ3TZlGSpaP3dHbNtie41HGugWrH\~8R\~h2OQ9l\~Dgx6JPrmz8Q\_\_\&amp;Key-Pair-Id=APKAJLOHF5GGSLRBV4ZA</t>
-        </is>
-      </c>
       <c r="BA68" t="n">
         <v>4</v>
       </c>
-      <c r="BB68" t="inlineStr">
-        <is>
-          <t>Bien documentado: Bosai Minerals adquirió Omai Bauxite Mining Inc. de IAMGOLD a fines de 2006 por USD 46M (una fuente indica USD 60M inversión total). El monto registrado de USD 60M corresponde a la inversión total incluyendo capital de trabajo inicial. Confirmado por South China Morning Post, Globe and Mail y sitio oficial de Bosai.</t>
-        </is>
-      </c>
-      <c r="BC68" t="n">
+      <c r="BB68" t="n">
         <v>0</v>
       </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>https://www.scmp.com/article/579301/bosai-wins-bidding-guyana-bauxite-mines</t>
+        </is>
+      </c>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>https://www.theglobeandmail.com/report-on-business/iamgold-sells-stake-in-omai-bauxite-mining/article1111859/</t>
+        </is>
+      </c>
       <c r="BE68" t="inlineStr">
-        <is>
-          <t>https://www.scmp.com/article/579301/bosai-wins-bidding-guyana-bauxite-mines</t>
-        </is>
-      </c>
-      <c r="BF68" t="inlineStr">
-        <is>
-          <t>https://www.theglobeandmail.com/report-on-business/iamgold-sells-stake-in-omai-bauxite-mining/article1111859/</t>
-        </is>
-      </c>
-      <c r="BG68" t="inlineStr">
         <is>
           <t>https://en.cqbosai.com/about/fzlc/</t>
         </is>
@@ -9740,7 +9254,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G69" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -9812,15 +9326,15 @@
       <c r="BA69" t="n">
         <v>3</v>
       </c>
-      <c r="BC69" t="n">
+      <c r="BB69" t="n">
         <v>0</v>
       </c>
-      <c r="BE69" t="inlineStr">
+      <c r="BC69" t="inlineStr">
         <is>
           <t>https://latinoamerica21.com/en/china-expands-its-presence-in-guyana/</t>
         </is>
       </c>
-      <c r="BF69" t="inlineStr">
+      <c r="BD69" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2026/05/08/guyana-n0-3-in-global-rankings-for-chinese-investment/</t>
         </is>
@@ -9829,11 +9343,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GUY-0003</t>
+          <t>GUY-0020</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9850,7 +9364,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -9888,12 +9402,12 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Puente binacional sobre el rio Corentyne Monto ejecutado a la fecha de auditoria: USD 0M.</t>
+          <t>Puente binacional sobre el rio Corentyne Monto ejecutado a la fecha de auditoria</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Binational 1.1 km bridge over the Corentyne River linking Guyana and Suriname, under a DBFOM public-private partnership. CRBC won with a bid of USD 236,173,962; Chinese financing was not yet approved. Amount disbursed as of the audit date: USD 0M.</t>
+          <t>Binational 1.1 km bridge over the Corentyne River linking Guyana and Suriname</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -9920,22 +9434,17 @@
         </is>
       </c>
       <c r="BA70" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC70" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>https://latinoamerica21.com/en/china-expands-its-presence-in-guyana/</t>
+        </is>
       </c>
       <c r="BD70" t="inlineStr">
-        <is>
-          <t>evidencia insuficiente (score &lt;3)</t>
-        </is>
-      </c>
-      <c r="BE70" t="inlineStr">
-        <is>
-          <t>https://latinoamerica21.com/en/china-expands-its-presence-in-guyana/</t>
-        </is>
-      </c>
-      <c r="BF70" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2026/05/08/guyana-n0-3-in-global-rankings-for-chinese-investment/</t>
         </is>
@@ -9944,11 +9453,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GUY-0003</t>
+          <t>GUY-0020</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9965,7 +9474,7 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="1" t="inlineStr">
         <is>
           <t>328</t>
         </is>
@@ -10003,12 +9512,12 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Puente binacional sobre el rio Corentyne Monto ejecutado a la fecha de auditoria: USD 0M.</t>
+          <t>Puente binacional sobre el rio Corentyne Monto ejecutado a la fecha de auditoria</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Binational 1.1 km bridge over the Corentyne River linking Guyana and Suriname, under a DBFOM public-private partnership. CRBC won with a bid of USD 236,173,962; Chinese financing was not yet approved. Amount disbursed as of the audit date: USD 0M.</t>
+          <t>Binational 1.1 km bridge over the Corentyne River linking Guyana and Suriname</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -10037,15 +9546,15 @@
       <c r="BA71" t="n">
         <v>3</v>
       </c>
-      <c r="BC71" t="n">
+      <c r="BB71" t="n">
         <v>0</v>
       </c>
-      <c r="BE71" t="inlineStr">
+      <c r="BC71" t="inlineStr">
         <is>
           <t>https://nationalinterest.org/blog/energy-world/suriname-china-and-the-new-cold-war</t>
         </is>
       </c>
-      <c r="BF71" t="inlineStr">
+      <c r="BD71" t="inlineStr">
         <is>
           <t>https://worldoil.com/magazine/2026/july/features/guyana-suriname-the-new-petro-state-corridor-takes-hold/</t>
         </is>

--- a/data/sources/countries/guyana.xlsx
+++ b/data/sources/countries/guyana.xlsx
@@ -46,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE71"/>
+  <dimension ref="A1:BI73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,22 +684,42 @@
       </c>
       <c r="BB1" t="inlineStr">
         <is>
+          <t>reliability_notes</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
           <t>cancelled</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>cancelled_motivo</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>source3</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>source4</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>source5</t>
         </is>
       </c>
     </row>
@@ -731,10 +750,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G2" t="n">
+        <v>328</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -783,8 +800,11 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>100</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -810,27 +830,57 @@
           <t>https://www.kaieteurnewsonline.com/2016/11/05/bosai-buys-matthews-ridge-manganese-project/</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
         <v>4</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
         <v>0</v>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2016/11/05/bosai-buys-matthews-ridge-manganese-project/</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>https://miningconnection.com/surface/news/article/bosai_minerals_to_acquire_reunion_golds_matthews_ridge_manganese_project_fo</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>https://nre.gov.gy/2017/03/21/board-of-directors-of-bosai-minerals-group-meet-with-government-to-update-on-plans-to-advance-new-manganese-project-in-matthews-ridge-region-1/</t>
         </is>
       </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -859,10 +909,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G3" t="n">
+        <v>328</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -913,6 +961,9 @@
       <c r="R3" t="n">
         <v>376</v>
       </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -938,27 +989,57 @@
           <t>https://www.cfr.org/backgrounder/chinas-huawei-threat-us-national-security</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
         <v>3</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="n">
         <v>0</v>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr">
         <is>
           <t>https://www.stabroeknews.com/2019/08/17/opinion/letters/concerned-about-implications-of-huawei-involvement-in-national-broadband-project/</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>https://www.guyanastandard.com/2019/12/07/chinese-company-working-on-guyanas-broadband-project-labelled-as-national-security-threat-by-us-regulators/</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>https://dpi.gov.gy/national-broadband-network-on-the-horizon/</t>
         </is>
       </c>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -987,10 +1068,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G4" t="n">
+        <v>328</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1039,8 +1118,11 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>2600</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1066,27 +1148,57 @@
           <t>https://dpi.gov.gy/us260m-demerara-river-bridge-64-per-cent-complete/</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
         <v>4</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="n">
         <v>0</v>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2022/05/26/us260m-contract-signed-for-new-demerara-river-bridge/</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>https://www.globalconstructionreview.com/china-railway-wins-260m-contract-to-build-demerara-river-bridge-in-guyana/</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>https://www.globaltimes.cn/page/202205/1266597.shtml</t>
         </is>
       </c>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1115,10 +1227,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G5" t="n">
+        <v>328</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1167,8 +1277,11 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>2600</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1194,27 +1307,57 @@
           <t>https://dpi.gov.gy/us260m-demerara-river-bridge-64-per-cent-complete/</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
         <v>4</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="n">
         <v>0</v>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2022/05/26/us260m-contract-signed-for-new-demerara-river-bridge/</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>https://www.globalconstructionreview.com/china-railway-wins-260m-contract-to-build-demerara-river-bridge-in-guyana/</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>https://www.globaltimes.cn/page/202205/1266597.shtml</t>
         </is>
       </c>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1243,10 +1386,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G6" t="n">
+        <v>328</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1295,8 +1436,11 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>2600</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1322,27 +1466,57 @@
           <t>https://dpi.gov.gy/us260m-demerara-river-bridge-64-per-cent-complete/</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
         <v>4</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
         <v>0</v>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2022/05/26/us260m-contract-signed-for-new-demerara-river-bridge/</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>https://www.globalconstructionreview.com/china-railway-wins-260m-contract-to-build-demerara-river-bridge-in-guyana/</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>https://www.globaltimes.cn/page/202205/1266597.shtml</t>
         </is>
       </c>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1371,10 +1545,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G7" t="n">
+        <v>328</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1423,8 +1595,11 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1450,27 +1625,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
         <v>4</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="n">
         <v>0</v>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1499,10 +1704,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G8" t="n">
+        <v>328</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1551,8 +1754,11 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1578,27 +1784,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
         <v>4</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="n">
         <v>0</v>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1627,10 +1863,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G9" t="n">
+        <v>328</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1679,8 +1913,11 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1706,27 +1943,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
         <v>4</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="n">
         <v>0</v>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1755,10 +2022,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G10" t="n">
+        <v>328</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1807,8 +2072,11 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1834,27 +2102,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
         <v>4</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="n">
         <v>0</v>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1883,10 +2181,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G11" t="n">
+        <v>328</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1935,8 +2231,11 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1962,27 +2261,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
         <v>4</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="n">
         <v>0</v>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2011,10 +2340,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G12" t="n">
+        <v>328</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -2063,8 +2390,11 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2090,27 +2420,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
         <v>4</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="n">
         <v>0</v>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2139,10 +2499,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G13" t="n">
+        <v>328</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2191,8 +2549,11 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2218,27 +2579,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
         <v>4</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="n">
         <v>0</v>
       </c>
-      <c r="BC13" t="inlineStr">
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD13" t="inlineStr">
+      <c r="BF13" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2267,10 +2658,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G14" t="n">
+        <v>328</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2319,8 +2708,11 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2346,27 +2738,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="n">
         <v>4</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="n">
         <v>0</v>
       </c>
-      <c r="BC14" t="inlineStr">
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD14" t="inlineStr">
+      <c r="BF14" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2395,10 +2817,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G15" t="n">
+        <v>328</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2447,8 +2867,11 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2474,27 +2897,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="n">
         <v>4</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="n">
         <v>0</v>
       </c>
-      <c r="BC15" t="inlineStr">
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD15" t="inlineStr">
+      <c r="BF15" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2523,10 +2976,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G16" t="n">
+        <v>328</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2575,8 +3026,11 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2602,27 +3056,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="n">
         <v>4</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="n">
         <v>0</v>
       </c>
-      <c r="BC16" t="inlineStr">
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD16" t="inlineStr">
+      <c r="BF16" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE16" t="inlineStr">
+      <c r="BG16" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2651,10 +3135,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G17" t="n">
+        <v>328</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2703,8 +3185,11 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2730,27 +3215,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="n">
         <v>4</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="n">
         <v>0</v>
       </c>
-      <c r="BC17" t="inlineStr">
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD17" t="inlineStr">
+      <c r="BF17" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE17" t="inlineStr">
+      <c r="BG17" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2779,10 +3294,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G18" t="n">
+        <v>328</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2831,8 +3344,11 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2858,27 +3374,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="n">
         <v>4</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="n">
         <v>0</v>
       </c>
-      <c r="BC18" t="inlineStr">
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD18" t="inlineStr">
+      <c r="BF18" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE18" t="inlineStr">
+      <c r="BG18" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2907,10 +3453,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G19" t="n">
+        <v>328</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2959,8 +3503,11 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -2986,27 +3533,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="n">
         <v>4</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="n">
         <v>0</v>
       </c>
-      <c r="BC19" t="inlineStr">
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD19" t="inlineStr">
+      <c r="BF19" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE19" t="inlineStr">
+      <c r="BG19" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3035,10 +3612,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G20" t="n">
+        <v>328</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -3087,8 +3662,11 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3114,27 +3692,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="n">
         <v>4</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="n">
         <v>0</v>
       </c>
-      <c r="BC20" t="inlineStr">
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD20" t="inlineStr">
+      <c r="BF20" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE20" t="inlineStr">
+      <c r="BG20" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3163,10 +3771,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G21" t="n">
+        <v>328</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -3215,8 +3821,11 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3242,27 +3851,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
       <c r="BA21" t="n">
         <v>4</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="n">
         <v>0</v>
       </c>
-      <c r="BC21" t="inlineStr">
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD21" t="inlineStr">
+      <c r="BF21" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE21" t="inlineStr">
+      <c r="BG21" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3291,10 +3930,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G22" t="n">
+        <v>328</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -3343,8 +3980,11 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3370,27 +4010,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
         <v>4</v>
       </c>
-      <c r="BB22" t="n">
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="n">
         <v>0</v>
       </c>
-      <c r="BC22" t="inlineStr">
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD22" t="inlineStr">
+      <c r="BF22" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE22" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3419,10 +4089,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G23" t="n">
+        <v>328</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3471,8 +4139,11 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3498,27 +4169,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
         <v>4</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="n">
         <v>0</v>
       </c>
-      <c r="BC23" t="inlineStr">
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD23" t="inlineStr">
+      <c r="BF23" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE23" t="inlineStr">
+      <c r="BG23" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3547,10 +4248,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G24" t="n">
+        <v>328</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -3599,8 +4298,11 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3626,27 +4328,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
         <v>4</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="n">
         <v>0</v>
       </c>
-      <c r="BC24" t="inlineStr">
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD24" t="inlineStr">
+      <c r="BF24" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE24" t="inlineStr">
+      <c r="BG24" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3675,10 +4407,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G25" t="n">
+        <v>328</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -3727,8 +4457,11 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3754,27 +4487,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="n">
         <v>4</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="n">
         <v>0</v>
       </c>
-      <c r="BC25" t="inlineStr">
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD25" t="inlineStr">
+      <c r="BF25" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE25" t="inlineStr">
+      <c r="BG25" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3803,10 +4566,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G26" t="n">
+        <v>328</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -3855,8 +4616,11 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -3882,27 +4646,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="n">
         <v>4</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="n">
         <v>0</v>
       </c>
-      <c r="BC26" t="inlineStr">
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD26" t="inlineStr">
+      <c r="BF26" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE26" t="inlineStr">
+      <c r="BG26" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3931,10 +4725,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G27" t="n">
+        <v>328</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -3983,8 +4775,11 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4010,27 +4805,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="n">
         <v>4</v>
       </c>
-      <c r="BB27" t="n">
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="n">
         <v>0</v>
       </c>
-      <c r="BC27" t="inlineStr">
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD27" t="inlineStr">
+      <c r="BF27" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE27" t="inlineStr">
+      <c r="BG27" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4059,10 +4884,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G28" t="n">
+        <v>328</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -4111,8 +4934,11 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4138,27 +4964,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="n">
         <v>4</v>
       </c>
-      <c r="BB28" t="n">
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="n">
         <v>0</v>
       </c>
-      <c r="BC28" t="inlineStr">
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD28" t="inlineStr">
+      <c r="BF28" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE28" t="inlineStr">
+      <c r="BG28" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4187,10 +5043,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G29" t="n">
+        <v>328</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -4239,8 +5093,11 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4266,27 +5123,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="n">
         <v>4</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="n">
         <v>0</v>
       </c>
-      <c r="BC29" t="inlineStr">
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD29" t="inlineStr">
+      <c r="BF29" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE29" t="inlineStr">
+      <c r="BG29" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4315,10 +5202,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G30" t="n">
+        <v>328</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -4367,8 +5252,11 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4394,27 +5282,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
         <v>4</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="n">
         <v>0</v>
       </c>
-      <c r="BC30" t="inlineStr">
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD30" t="inlineStr">
+      <c r="BF30" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE30" t="inlineStr">
+      <c r="BG30" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4443,10 +5361,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G31" t="n">
+        <v>328</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -4495,8 +5411,11 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4522,27 +5441,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
         <v>4</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="n">
         <v>0</v>
       </c>
-      <c r="BC31" t="inlineStr">
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD31" t="inlineStr">
+      <c r="BF31" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE31" t="inlineStr">
+      <c r="BG31" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4571,10 +5520,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G32" t="n">
+        <v>328</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -4623,8 +5570,11 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4650,27 +5600,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
         <v>4</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="n">
         <v>0</v>
       </c>
-      <c r="BC32" t="inlineStr">
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD32" t="inlineStr">
+      <c r="BF32" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE32" t="inlineStr">
+      <c r="BG32" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4699,10 +5679,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G33" t="n">
+        <v>328</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -4751,8 +5729,11 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4778,27 +5759,57 @@
           <t>https://www.kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
         <v>4</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BB33" t="inlineStr"/>
+      <c r="BC33" t="n">
         <v>0</v>
       </c>
-      <c r="BC33" t="inlineStr">
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD33" t="inlineStr">
+      <c r="BF33" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE33" t="inlineStr">
+      <c r="BG33" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4827,10 +5838,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G34" t="n">
+        <v>328</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -4881,6 +5890,9 @@
       <c r="R34" t="n">
         <v>1019</v>
       </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -4906,27 +5918,57 @@
           <t>https://kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
         <v>3</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BB34" t="inlineStr"/>
+      <c r="BC34" t="n">
         <v>0</v>
       </c>
-      <c r="BC34" t="inlineStr">
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
-      <c r="BD34" t="inlineStr">
+      <c r="BF34" t="inlineStr">
         <is>
           <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
         </is>
       </c>
-      <c r="BE34" t="inlineStr">
+      <c r="BG34" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
       </c>
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4955,10 +5997,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G35" t="n">
+        <v>328</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -5009,6 +6049,9 @@
       <c r="R35" t="n">
         <v>1019</v>
       </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5034,27 +6077,57 @@
           <t>https://kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
         <v>3</v>
       </c>
-      <c r="BB35" t="n">
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="n">
         <v>0</v>
       </c>
-      <c r="BC35" t="inlineStr">
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
-      <c r="BD35" t="inlineStr">
+      <c r="BF35" t="inlineStr">
         <is>
           <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
         </is>
       </c>
-      <c r="BE35" t="inlineStr">
+      <c r="BG35" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
       </c>
+      <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5083,10 +6156,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G36" t="n">
+        <v>328</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -5137,6 +6208,9 @@
       <c r="R36" t="n">
         <v>1019</v>
       </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5162,27 +6236,57 @@
           <t>https://kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
         <v>3</v>
       </c>
-      <c r="BB36" t="n">
+      <c r="BB36" t="inlineStr"/>
+      <c r="BC36" t="n">
         <v>0</v>
       </c>
-      <c r="BC36" t="inlineStr">
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
-      <c r="BD36" t="inlineStr">
+      <c r="BF36" t="inlineStr">
         <is>
           <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
         </is>
       </c>
-      <c r="BE36" t="inlineStr">
+      <c r="BG36" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
       </c>
+      <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5211,10 +6315,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G37" t="n">
+        <v>328</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -5265,6 +6367,9 @@
       <c r="R37" t="n">
         <v>1019</v>
       </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5290,27 +6395,57 @@
           <t>https://kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
         <v>3</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="n">
         <v>0</v>
       </c>
-      <c r="BC37" t="inlineStr">
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
-      <c r="BD37" t="inlineStr">
+      <c r="BF37" t="inlineStr">
         <is>
           <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
         </is>
       </c>
-      <c r="BE37" t="inlineStr">
+      <c r="BG37" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
       </c>
+      <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5339,10 +6474,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G38" t="n">
+        <v>328</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -5393,6 +6526,9 @@
       <c r="R38" t="n">
         <v>1019</v>
       </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5418,27 +6554,57 @@
           <t>https://kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr"/>
+      <c r="AX38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
         <v>3</v>
       </c>
-      <c r="BB38" t="n">
+      <c r="BB38" t="inlineStr"/>
+      <c r="BC38" t="n">
         <v>0</v>
       </c>
-      <c r="BC38" t="inlineStr">
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
-      <c r="BD38" t="inlineStr">
+      <c r="BF38" t="inlineStr">
         <is>
           <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
         </is>
       </c>
-      <c r="BE38" t="inlineStr">
+      <c r="BG38" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
       </c>
+      <c r="BH38" t="inlineStr"/>
+      <c r="BI38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5467,10 +6633,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G39" t="n">
+        <v>328</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -5521,6 +6685,9 @@
       <c r="R39" t="n">
         <v>1019</v>
       </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5546,27 +6713,57 @@
           <t>https://kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
         <v>3</v>
       </c>
-      <c r="BB39" t="n">
+      <c r="BB39" t="inlineStr"/>
+      <c r="BC39" t="n">
         <v>0</v>
       </c>
-      <c r="BC39" t="inlineStr">
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
-      <c r="BD39" t="inlineStr">
+      <c r="BF39" t="inlineStr">
         <is>
           <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
         </is>
       </c>
-      <c r="BE39" t="inlineStr">
+      <c r="BG39" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
       </c>
+      <c r="BH39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5595,10 +6792,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G40" t="n">
+        <v>328</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -5649,6 +6844,9 @@
       <c r="R40" t="n">
         <v>1019</v>
       </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5674,27 +6872,57 @@
           <t>https://kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
         <v>3</v>
       </c>
-      <c r="BB40" t="n">
+      <c r="BB40" t="inlineStr"/>
+      <c r="BC40" t="n">
         <v>0</v>
       </c>
-      <c r="BC40" t="inlineStr">
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
-      <c r="BD40" t="inlineStr">
+      <c r="BF40" t="inlineStr">
         <is>
           <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
         </is>
       </c>
-      <c r="BE40" t="inlineStr">
+      <c r="BG40" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
       </c>
+      <c r="BH40" t="inlineStr"/>
+      <c r="BI40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5723,10 +6951,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G41" t="n">
+        <v>328</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -5777,6 +7003,9 @@
       <c r="R41" t="n">
         <v>1019</v>
       </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5802,27 +7031,57 @@
           <t>https://kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
         <v>3</v>
       </c>
-      <c r="BB41" t="n">
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="n">
         <v>0</v>
       </c>
-      <c r="BC41" t="inlineStr">
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
-      <c r="BD41" t="inlineStr">
+      <c r="BF41" t="inlineStr">
         <is>
           <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
         </is>
       </c>
-      <c r="BE41" t="inlineStr">
+      <c r="BG41" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
       </c>
+      <c r="BH41" t="inlineStr"/>
+      <c r="BI41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5851,10 +7110,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G42" t="n">
+        <v>328</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -5905,6 +7162,9 @@
       <c r="R42" t="n">
         <v>1019</v>
       </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -5930,27 +7190,57 @@
           <t>https://kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr"/>
+      <c r="AX42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
         <v>3</v>
       </c>
-      <c r="BB42" t="n">
+      <c r="BB42" t="inlineStr"/>
+      <c r="BC42" t="n">
         <v>0</v>
       </c>
-      <c r="BC42" t="inlineStr">
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
-      <c r="BD42" t="inlineStr">
+      <c r="BF42" t="inlineStr">
         <is>
           <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
         </is>
       </c>
-      <c r="BE42" t="inlineStr">
+      <c r="BG42" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
       </c>
+      <c r="BH42" t="inlineStr"/>
+      <c r="BI42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5979,10 +7269,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G43" t="n">
+        <v>328</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -6033,6 +7321,9 @@
       <c r="R43" t="n">
         <v>1019</v>
       </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6058,27 +7349,57 @@
           <t>https://kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
         <v>3</v>
       </c>
-      <c r="BB43" t="n">
+      <c r="BB43" t="inlineStr"/>
+      <c r="BC43" t="n">
         <v>0</v>
       </c>
-      <c r="BC43" t="inlineStr">
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
-      <c r="BD43" t="inlineStr">
+      <c r="BF43" t="inlineStr">
         <is>
           <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
         </is>
       </c>
-      <c r="BE43" t="inlineStr">
+      <c r="BG43" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
       </c>
+      <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6107,10 +7428,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G44" t="n">
+        <v>328</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -6161,6 +7480,9 @@
       <c r="R44" t="n">
         <v>1019</v>
       </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6186,27 +7508,57 @@
           <t>https://kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr"/>
+      <c r="AX44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
         <v>3</v>
       </c>
-      <c r="BB44" t="n">
+      <c r="BB44" t="inlineStr"/>
+      <c r="BC44" t="n">
         <v>0</v>
       </c>
-      <c r="BC44" t="inlineStr">
+      <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
-      <c r="BD44" t="inlineStr">
+      <c r="BF44" t="inlineStr">
         <is>
           <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
         </is>
       </c>
-      <c r="BE44" t="inlineStr">
+      <c r="BG44" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
       </c>
+      <c r="BH44" t="inlineStr"/>
+      <c r="BI44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6235,10 +7587,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G45" t="n">
+        <v>328</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -6289,6 +7639,9 @@
       <c r="R45" t="n">
         <v>1019</v>
       </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6314,27 +7667,57 @@
           <t>https://kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr"/>
       <c r="BA45" t="n">
         <v>3</v>
       </c>
-      <c r="BB45" t="n">
+      <c r="BB45" t="inlineStr"/>
+      <c r="BC45" t="n">
         <v>0</v>
       </c>
-      <c r="BC45" t="inlineStr">
+      <c r="BD45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr">
         <is>
           <t>https://www.kaieteurnewsonline.com/2021/12/23/chinese-company-among-12-contractors-to-build-13-3-b-eccles-to-diamond-4-lane-road/</t>
         </is>
       </c>
-      <c r="BD45" t="inlineStr">
+      <c r="BF45" t="inlineStr">
         <is>
           <t>https://mohw.gov.gy/2021/12/22/13-3-billion-in-contracts-inked-for-eccles-to-diamond-four-lane-highway/</t>
         </is>
       </c>
-      <c r="BE45" t="inlineStr">
+      <c r="BG45" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/13-3b-eccles-to-diamond-4-lane-highway-to-open-next-month-min-croal/</t>
         </is>
       </c>
+      <c r="BH45" t="inlineStr"/>
+      <c r="BI45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6363,10 +7746,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G46" t="n">
+        <v>328</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -6417,6 +7798,9 @@
       <c r="R46" t="n">
         <v>3977</v>
       </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6442,27 +7826,57 @@
           <t>https://www.powerchina-intl.com/show/9/80.html</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr"/>
+      <c r="AX46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr"/>
       <c r="BA46" t="n">
         <v>3</v>
       </c>
-      <c r="BB46" t="n">
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="n">
         <v>0</v>
       </c>
-      <c r="BC46" t="inlineStr">
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-inked-with-chinese-firm-for-water-treatment-plants/</t>
         </is>
       </c>
-      <c r="BD46" t="inlineStr">
+      <c r="BF46" t="inlineStr">
         <is>
           <t>https://en.powerchina.cn/2020-02/25/c_714175.htm</t>
         </is>
       </c>
-      <c r="BE46" t="inlineStr">
+      <c r="BG46" t="inlineStr">
         <is>
           <t>https://www.stabroeknews.com/2017/09/01/news/guyana/chinese-company-to-construct-three-water-plants/</t>
         </is>
       </c>
+      <c r="BH46" t="inlineStr"/>
+      <c r="BI46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6491,10 +7905,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G47" t="n">
+        <v>328</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -6545,6 +7957,9 @@
       <c r="R47" t="n">
         <v>3977</v>
       </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6570,27 +7985,57 @@
           <t>https://www.powerchina-intl.com/show/9/80.html</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
       <c r="BA47" t="n">
         <v>3</v>
       </c>
-      <c r="BB47" t="n">
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="n">
         <v>0</v>
       </c>
-      <c r="BC47" t="inlineStr">
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-inked-with-chinese-firm-for-water-treatment-plants/</t>
         </is>
       </c>
-      <c r="BD47" t="inlineStr">
+      <c r="BF47" t="inlineStr">
         <is>
           <t>https://en.powerchina.cn/2020-02/25/c_714175.htm</t>
         </is>
       </c>
-      <c r="BE47" t="inlineStr">
+      <c r="BG47" t="inlineStr">
         <is>
           <t>https://www.stabroeknews.com/2017/09/01/news/guyana/chinese-company-to-construct-three-water-plants/</t>
         </is>
       </c>
+      <c r="BH47" t="inlineStr"/>
+      <c r="BI47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6619,10 +8064,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G48" t="n">
+        <v>328</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -6673,6 +8116,9 @@
       <c r="R48" t="n">
         <v>3977</v>
       </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6698,27 +8144,57 @@
           <t>https://www.powerchina-intl.com/show/9/80.html</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr"/>
       <c r="BA48" t="n">
         <v>3</v>
       </c>
-      <c r="BB48" t="n">
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="n">
         <v>0</v>
       </c>
-      <c r="BC48" t="inlineStr">
+      <c r="BD48" t="inlineStr"/>
+      <c r="BE48" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-inked-with-chinese-firm-for-water-treatment-plants/</t>
         </is>
       </c>
-      <c r="BD48" t="inlineStr">
+      <c r="BF48" t="inlineStr">
         <is>
           <t>https://en.powerchina.cn/2020-02/25/c_714175.htm</t>
         </is>
       </c>
-      <c r="BE48" t="inlineStr">
+      <c r="BG48" t="inlineStr">
         <is>
           <t>https://www.stabroeknews.com/2017/09/01/news/guyana/chinese-company-to-construct-three-water-plants/</t>
         </is>
       </c>
+      <c r="BH48" t="inlineStr"/>
+      <c r="BI48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6747,10 +8223,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G49" t="n">
+        <v>328</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -6801,6 +8275,9 @@
       <c r="R49" t="n">
         <v>372</v>
       </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6826,27 +8303,57 @@
           <t>https://health.gov.gy/health-on-the-move/regional-hospitals/</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
         <v>3</v>
       </c>
-      <c r="BB49" t="n">
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="n">
         <v>0</v>
       </c>
-      <c r="BC49" t="inlineStr">
+      <c r="BD49" t="inlineStr"/>
+      <c r="BE49" t="inlineStr">
         <is>
           <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
         </is>
       </c>
-      <c r="BD49" t="inlineStr">
+      <c r="BF49" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
         </is>
       </c>
-      <c r="BE49" t="inlineStr">
+      <c r="BG49" t="inlineStr">
         <is>
           <t>https://www.sinomach.com.cn/en/MediaCenter/News/202509/t20250919_580641.html</t>
         </is>
       </c>
+      <c r="BH49" t="inlineStr"/>
+      <c r="BI49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6875,10 +8382,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G50" t="n">
+        <v>328</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -6929,6 +8434,9 @@
       <c r="R50" t="n">
         <v>372</v>
       </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -6954,27 +8462,57 @@
           <t>https://health.gov.gy/health-on-the-move/regional-hospitals/</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
         <v>3</v>
       </c>
-      <c r="BB50" t="n">
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="n">
         <v>0</v>
       </c>
-      <c r="BC50" t="inlineStr">
+      <c r="BD50" t="inlineStr"/>
+      <c r="BE50" t="inlineStr">
         <is>
           <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
         </is>
       </c>
-      <c r="BD50" t="inlineStr">
+      <c r="BF50" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
         </is>
       </c>
-      <c r="BE50" t="inlineStr">
+      <c r="BG50" t="inlineStr">
         <is>
           <t>https://www.sinomach.com.cn/en/MediaCenter/News/202509/t20250919_580641.html</t>
         </is>
       </c>
+      <c r="BH50" t="inlineStr"/>
+      <c r="BI50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7003,10 +8541,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G51" t="n">
+        <v>328</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -7057,6 +8593,9 @@
       <c r="R51" t="n">
         <v>372</v>
       </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7082,27 +8621,57 @@
           <t>https://health.gov.gy/health-on-the-move/regional-hospitals/</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
         <v>3</v>
       </c>
-      <c r="BB51" t="n">
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="n">
         <v>0</v>
       </c>
-      <c r="BC51" t="inlineStr">
+      <c r="BD51" t="inlineStr"/>
+      <c r="BE51" t="inlineStr">
         <is>
           <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
         </is>
       </c>
-      <c r="BD51" t="inlineStr">
+      <c r="BF51" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
         </is>
       </c>
-      <c r="BE51" t="inlineStr">
+      <c r="BG51" t="inlineStr">
         <is>
           <t>https://www.sinomach.com.cn/en/MediaCenter/News/202509/t20250919_580641.html</t>
         </is>
       </c>
+      <c r="BH51" t="inlineStr"/>
+      <c r="BI51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7131,10 +8700,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G52" t="n">
+        <v>328</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -7185,6 +8752,9 @@
       <c r="R52" t="n">
         <v>372</v>
       </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7210,27 +8780,57 @@
           <t>https://health.gov.gy/health-on-the-move/regional-hospitals/</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
         <v>3</v>
       </c>
-      <c r="BB52" t="n">
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="n">
         <v>0</v>
       </c>
-      <c r="BC52" t="inlineStr">
+      <c r="BD52" t="inlineStr"/>
+      <c r="BE52" t="inlineStr">
         <is>
           <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
         </is>
       </c>
-      <c r="BD52" t="inlineStr">
+      <c r="BF52" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
         </is>
       </c>
-      <c r="BE52" t="inlineStr">
+      <c r="BG52" t="inlineStr">
         <is>
           <t>https://www.sinomach.com.cn/en/MediaCenter/News/202509/t20250919_580641.html</t>
         </is>
       </c>
+      <c r="BH52" t="inlineStr"/>
+      <c r="BI52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7259,10 +8859,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G53" t="n">
+        <v>328</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -7313,6 +8911,9 @@
       <c r="R53" t="n">
         <v>372</v>
       </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7338,27 +8939,57 @@
           <t>https://health.gov.gy/health-on-the-move/regional-hospitals/</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
         <v>3</v>
       </c>
-      <c r="BB53" t="n">
+      <c r="BB53" t="inlineStr"/>
+      <c r="BC53" t="n">
         <v>0</v>
       </c>
-      <c r="BC53" t="inlineStr">
+      <c r="BD53" t="inlineStr"/>
+      <c r="BE53" t="inlineStr">
         <is>
           <t>https://guyanachronicle.com/2022/09/18/sinopharm-to-build-six-new-regional-hospitals-in-guyana/</t>
         </is>
       </c>
-      <c r="BD53" t="inlineStr">
+      <c r="BF53" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/09/16/chinas-sinopharm-to-construct-six-new-hospitals-in-guyana/</t>
         </is>
       </c>
-      <c r="BE53" t="inlineStr">
+      <c r="BG53" t="inlineStr">
         <is>
           <t>https://www.sinomach.com.cn/en/MediaCenter/News/202509/t20250919_580641.html</t>
         </is>
       </c>
+      <c r="BH53" t="inlineStr"/>
+      <c r="BI53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7387,10 +9018,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G54" t="n">
+        <v>328</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -7441,6 +9070,9 @@
       <c r="R54" t="n">
         <v>12</v>
       </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7466,17 +9098,53 @@
           <t>https://www.cnqc.com/html/web/fuwuzhongxin/zhaobiaoxinxi/18088.html</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="inlineStr"/>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AU54" t="inlineStr"/>
+      <c r="AV54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr"/>
+      <c r="AX54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
         <v>0</v>
       </c>
-      <c r="BB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC54" t="inlineStr">
+      <c r="BB54" t="inlineStr"/>
+      <c r="BC54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE54" t="inlineStr">
         <is>
           <t>https://guyanachronicle.com/2020/11/25/450570/</t>
         </is>
       </c>
+      <c r="BF54" t="inlineStr"/>
+      <c r="BG54" t="inlineStr"/>
+      <c r="BH54" t="inlineStr"/>
+      <c r="BI54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7505,10 +9173,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G55" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G55" t="n">
+        <v>328</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -7557,8 +9223,11 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>1380</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7614,27 +9283,55 @@
           <t>https://china.aiddata.org/projects/36574/</t>
         </is>
       </c>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="inlineStr"/>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AU55" t="inlineStr"/>
+      <c r="AV55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr"/>
+      <c r="AX55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
         <v>4</v>
       </c>
-      <c r="BB55" t="n">
+      <c r="BB55" t="inlineStr"/>
+      <c r="BC55" t="n">
         <v>0</v>
       </c>
-      <c r="BC55" t="inlineStr">
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>https://latinoamerica21.com/en/china-expands-its-presence-in-guyana/</t>
+        </is>
+      </c>
+      <c r="BE55" t="inlineStr">
         <is>
           <t>https://www.caribjournal.com/2011/11/19/guyanas-cabinet-approves-138-million-airport-expansion-deal-with-china/</t>
         </is>
       </c>
-      <c r="BD55" t="inlineStr">
+      <c r="BF55" t="inlineStr">
         <is>
           <t>https://www.airport-technology.com/projects/cheddi-jagan-international-airport-expansion-guyana/</t>
         </is>
       </c>
-      <c r="BE55" t="inlineStr">
+      <c r="BG55" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/36574/</t>
         </is>
       </c>
+      <c r="BH55" t="inlineStr"/>
+      <c r="BI55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7663,10 +9360,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G56" t="n">
+        <v>328</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -7717,6 +9412,9 @@
       <c r="R56" t="n">
         <v>53</v>
       </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -7752,6 +9450,8 @@
           <t>https://archives.datapages.com/data/specpubs/memoir125/data/433_aapg-sp2150433.htm</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
       <c r="AE56" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. ft.com.</t>
@@ -7762,22 +9462,55 @@
           <t>https://www.ft.com/content/3ad64602-88cc-4d4c-ad5e-20993b929bc3</t>
         </is>
       </c>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="inlineStr"/>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AU56" t="inlineStr"/>
+      <c r="AV56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr"/>
+      <c r="AX56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC56" t="inlineStr">
-        <is>
-          <t>https://budsoffshoreenergy.com/2024/03/25/how-china-became-a-factor-in-the-stabroek-guyana-dispute/</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>Confirmado que CNOOC adquirió 25% del bloque Stabroek en 2014 a través de su subsidiaria Nexen (adquirida de Canadá en 2013). La entrada registra '10\*' como monto (inversión nominal o no cuantificada), lo cual es coherente con que la participación fue heredada de la compra de Nexen y no una transacción separada directa en Guyana. La operación está bien documentada aunque el monto específico no es claro.</t>
+        </is>
+      </c>
+      <c r="BC56" t="n">
+        <v>1</v>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
+          <t>evidencia insuficiente (score &lt;3)</t>
+        </is>
+      </c>
+      <c r="BE56" t="inlineStr">
+        <is>
+          <t>https://latinoamerica21.com/en/china-expands-its-presence-in-guyana/</t>
+        </is>
+      </c>
+      <c r="BF56" t="inlineStr">
+        <is>
           <t>https://www.velaw.com/insights/the-stabroek-joa-arbitration-is-it-time-to-revisit-joa-change-in-control-provisions/</t>
         </is>
       </c>
+      <c r="BG56" t="inlineStr"/>
+      <c r="BH56" t="inlineStr"/>
+      <c r="BI56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7806,10 +9539,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G57" t="n">
+        <v>328</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -7858,8 +9589,11 @@
         </is>
       </c>
       <c r="R57" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7875,27 +9609,59 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr"/>
+      <c r="AQ57" t="inlineStr"/>
+      <c r="AR57" t="inlineStr"/>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AU57" t="inlineStr"/>
+      <c r="AV57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr"/>
+      <c r="AX57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
         <v>4</v>
       </c>
-      <c r="BB57" t="n">
+      <c r="BB57" t="inlineStr"/>
+      <c r="BC57" t="n">
         <v>0</v>
       </c>
-      <c r="BC57" t="inlineStr">
+      <c r="BD57" t="inlineStr"/>
+      <c r="BE57" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD57" t="inlineStr">
+      <c r="BF57" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE57" t="inlineStr">
+      <c r="BG57" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH57" t="inlineStr"/>
+      <c r="BI57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7924,10 +9690,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G58" t="n">
+        <v>328</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -7976,8 +9740,11 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -7993,27 +9760,59 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr"/>
+      <c r="AQ58" t="inlineStr"/>
+      <c r="AR58" t="inlineStr"/>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AU58" t="inlineStr"/>
+      <c r="AV58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr"/>
+      <c r="AX58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
         <v>4</v>
       </c>
-      <c r="BB58" t="n">
+      <c r="BB58" t="inlineStr"/>
+      <c r="BC58" t="n">
         <v>0</v>
       </c>
-      <c r="BC58" t="inlineStr">
+      <c r="BD58" t="inlineStr"/>
+      <c r="BE58" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD58" t="inlineStr">
+      <c r="BF58" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE58" t="inlineStr">
+      <c r="BG58" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH58" t="inlineStr"/>
+      <c r="BI58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8042,10 +9841,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G59" t="n">
+        <v>328</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -8094,8 +9891,11 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8111,27 +9911,59 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr"/>
+      <c r="AQ59" t="inlineStr"/>
+      <c r="AR59" t="inlineStr"/>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AU59" t="inlineStr"/>
+      <c r="AV59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr"/>
+      <c r="AX59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr"/>
       <c r="BA59" t="n">
         <v>4</v>
       </c>
-      <c r="BB59" t="n">
+      <c r="BB59" t="inlineStr"/>
+      <c r="BC59" t="n">
         <v>0</v>
       </c>
-      <c r="BC59" t="inlineStr">
+      <c r="BD59" t="inlineStr"/>
+      <c r="BE59" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD59" t="inlineStr">
+      <c r="BF59" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE59" t="inlineStr">
+      <c r="BG59" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH59" t="inlineStr"/>
+      <c r="BI59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8160,10 +9992,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G60" t="n">
+        <v>328</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -8212,8 +10042,11 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8229,27 +10062,59 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
+      <c r="AQ60" t="inlineStr"/>
+      <c r="AR60" t="inlineStr"/>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AU60" t="inlineStr"/>
+      <c r="AV60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr"/>
+      <c r="AX60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
         <v>4</v>
       </c>
-      <c r="BB60" t="n">
+      <c r="BB60" t="inlineStr"/>
+      <c r="BC60" t="n">
         <v>0</v>
       </c>
-      <c r="BC60" t="inlineStr">
+      <c r="BD60" t="inlineStr"/>
+      <c r="BE60" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD60" t="inlineStr">
+      <c r="BF60" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE60" t="inlineStr">
+      <c r="BG60" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH60" t="inlineStr"/>
+      <c r="BI60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8278,10 +10143,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G61" t="n">
+        <v>328</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -8330,8 +10193,11 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>1840</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8347,27 +10213,59 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
+      <c r="AQ61" t="inlineStr"/>
+      <c r="AR61" t="inlineStr"/>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="inlineStr"/>
+      <c r="AV61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="n">
         <v>4</v>
       </c>
-      <c r="BB61" t="n">
+      <c r="BB61" t="inlineStr"/>
+      <c r="BC61" t="n">
         <v>0</v>
       </c>
-      <c r="BC61" t="inlineStr">
+      <c r="BD61" t="inlineStr"/>
+      <c r="BE61" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2022/10/15/chinese-company-awarded-us184m-contract-for-east-coast-road-project/</t>
         </is>
       </c>
-      <c r="BD61" t="inlineStr">
+      <c r="BF61" t="inlineStr">
         <is>
           <t>https://newsroom.gy/2022/10/15/contractor-begins-mobilisation-for-new-us184m-east-coast-railway-embankment-highway/</t>
         </is>
       </c>
-      <c r="BE61" t="inlineStr">
+      <c r="BG61" t="inlineStr">
         <is>
           <t>https://guyanatimesgy.com/contract-signed-for-us184m-railway-embankment-expansion/</t>
         </is>
       </c>
+      <c r="BH61" t="inlineStr"/>
+      <c r="BI61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8396,10 +10294,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G62" t="n">
+        <v>328</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -8450,6 +10346,9 @@
       <c r="R62" t="n">
         <v>238</v>
       </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -8465,27 +10364,59 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr"/>
+      <c r="AQ62" t="inlineStr"/>
+      <c r="AR62" t="inlineStr"/>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AU62" t="inlineStr"/>
+      <c r="AV62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr"/>
+      <c r="AX62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="n">
         <v>5</v>
       </c>
-      <c r="BB62" t="n">
+      <c r="BB62" t="inlineStr"/>
+      <c r="BC62" t="n">
         <v>0</v>
       </c>
-      <c r="BC62" t="inlineStr">
+      <c r="BD62" t="inlineStr"/>
+      <c r="BE62" t="inlineStr">
         <is>
           <t>https://www.mining-technology.com/news/zijin-mining-acquire-guyana-goldfields/</t>
         </is>
       </c>
-      <c r="BD62" t="inlineStr">
+      <c r="BF62" t="inlineStr">
         <is>
           <t>https://www.zijinmining.com/news/news-detail-119059.htm</t>
         </is>
       </c>
-      <c r="BE62" t="inlineStr">
+      <c r="BG62" t="inlineStr">
         <is>
           <t>https://guyanachronicle.com/2020/06/12/chinese-firm-zijin-mining-acquires-guyana-goldfields-in-cdn323m-deal/</t>
         </is>
       </c>
+      <c r="BH62" t="inlineStr"/>
+      <c r="BI62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8514,10 +10445,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G63" t="n">
+        <v>328</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -8568,6 +10497,9 @@
       <c r="R63" t="n">
         <v>25</v>
       </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -8583,27 +10515,59 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
+      <c r="AP63" t="inlineStr"/>
+      <c r="AQ63" t="inlineStr"/>
+      <c r="AR63" t="inlineStr"/>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AU63" t="inlineStr"/>
+      <c r="AV63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr"/>
+      <c r="AX63" t="inlineStr"/>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
         <v>3</v>
       </c>
-      <c r="BB63" t="n">
+      <c r="BB63" t="inlineStr"/>
+      <c r="BC63" t="n">
         <v>0</v>
       </c>
-      <c r="BC63" t="inlineStr">
+      <c r="BD63" t="inlineStr"/>
+      <c r="BE63" t="inlineStr">
         <is>
           <t>https://www.stabroeknews.com/2022/04/28/news/guyana/shell-mohamed-signs-us25m-pact-with-chec-for-quarry/</t>
         </is>
       </c>
-      <c r="BD63" t="inlineStr">
+      <c r="BF63" t="inlineStr">
         <is>
           <t>https://inewsguyana.com/hadis-world-chec-partner-to-supply-1-million-tonnes-of-aggregates-yearly/</t>
         </is>
       </c>
-      <c r="BE63" t="inlineStr">
+      <c r="BG63" t="inlineStr">
         <is>
           <t>https://inewsguyana.com/mohameds-enterprise-partners-with-chinese-firm-for-us25m-quarry-project/</t>
         </is>
       </c>
+      <c r="BH63" t="inlineStr"/>
+      <c r="BI63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8632,10 +10596,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G64" t="n">
+        <v>328</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -8686,6 +10648,9 @@
       <c r="R64" t="n">
         <v>25</v>
       </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -8701,27 +10666,59 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
+      <c r="AP64" t="inlineStr"/>
+      <c r="AQ64" t="inlineStr"/>
+      <c r="AR64" t="inlineStr"/>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AU64" t="inlineStr"/>
+      <c r="AV64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr"/>
+      <c r="AX64" t="inlineStr"/>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
         <v>3</v>
       </c>
-      <c r="BB64" t="n">
+      <c r="BB64" t="inlineStr"/>
+      <c r="BC64" t="n">
         <v>0</v>
       </c>
-      <c r="BC64" t="inlineStr">
+      <c r="BD64" t="inlineStr"/>
+      <c r="BE64" t="inlineStr">
         <is>
           <t>https://www.stabroeknews.com/2022/04/28/news/guyana/shell-mohamed-signs-us25m-pact-with-chec-for-quarry/</t>
         </is>
       </c>
-      <c r="BD64" t="inlineStr">
+      <c r="BF64" t="inlineStr">
         <is>
           <t>https://inewsguyana.com/hadis-world-chec-partner-to-supply-1-million-tonnes-of-aggregates-yearly/</t>
         </is>
       </c>
-      <c r="BE64" t="inlineStr">
+      <c r="BG64" t="inlineStr">
         <is>
           <t>https://inewsguyana.com/mohameds-enterprise-partners-with-chinese-firm-for-us25m-quarry-project/</t>
         </is>
       </c>
+      <c r="BH64" t="inlineStr"/>
+      <c r="BI64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8750,10 +10747,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G65" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G65" t="n">
+        <v>328</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -8804,6 +10799,9 @@
       <c r="R65" t="n">
         <v>25</v>
       </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
           <t>Greenfield</t>
@@ -8819,27 +10817,59 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr"/>
+      <c r="AQ65" t="inlineStr"/>
+      <c r="AR65" t="inlineStr"/>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AU65" t="inlineStr"/>
+      <c r="AV65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr"/>
+      <c r="AX65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="n">
         <v>3</v>
       </c>
-      <c r="BB65" t="n">
+      <c r="BB65" t="inlineStr"/>
+      <c r="BC65" t="n">
         <v>0</v>
       </c>
-      <c r="BC65" t="inlineStr">
+      <c r="BD65" t="inlineStr"/>
+      <c r="BE65" t="inlineStr">
         <is>
           <t>https://www.stabroeknews.com/2022/04/28/news/guyana/shell-mohamed-signs-us25m-pact-with-chec-for-quarry/</t>
         </is>
       </c>
-      <c r="BD65" t="inlineStr">
+      <c r="BF65" t="inlineStr">
         <is>
           <t>https://inewsguyana.com/hadis-world-chec-partner-to-supply-1-million-tonnes-of-aggregates-yearly/</t>
         </is>
       </c>
-      <c r="BE65" t="inlineStr">
+      <c r="BG65" t="inlineStr">
         <is>
           <t>https://inewsguyana.com/mohameds-enterprise-partners-with-chinese-firm-for-us25m-quarry-project/</t>
         </is>
       </c>
+      <c r="BH65" t="inlineStr"/>
+      <c r="BI65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8868,10 +10898,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G66" t="n">
+        <v>328</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -8922,6 +10950,9 @@
       <c r="R66" t="n">
         <v>49</v>
       </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -8947,6 +10978,10 @@
           <t>https://www.cnki.net/KCMS/detail/detail.aspx?dbcode=CJFD&amp;dbname=CJFDLAST2022&amp;filename=GXZT202203011&amp;uniplatform=OVERSEA&amp;v=hlu0ySpMhIW51We_35WIk-spUerUyXhlOZvj2Y8FWjU_C6xneEukFSQAf31madmo</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="inlineStr">
         <is>
           <t>Unknown. (2024). [Article]. china.aiddata.org.</t>
@@ -8957,27 +10992,55 @@
           <t>https://china.aiddata.org/projects/55943/</t>
         </is>
       </c>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
+      <c r="AP66" t="inlineStr"/>
+      <c r="AQ66" t="inlineStr"/>
+      <c r="AR66" t="inlineStr"/>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AU66" t="inlineStr"/>
+      <c r="AV66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr"/>
+      <c r="AX66" t="inlineStr"/>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr"/>
       <c r="BA66" t="n">
         <v>4</v>
       </c>
-      <c r="BB66" t="n">
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>Bien documentado: CNTIC Trading firmó contrato comercial el 22 de junio de 2004 con GuySuCo para el Proyecto de Modernización Azucarera de Skeldon. El costo final fue \~USD 187-200M, no USD 49M. El monto de USD 49M podría corresponder al préstamo concesional del EXIM Bank de China (RMB 270M = \~USD 40-49M), no al costo total. Proyecto terminado en 2009, confirmado por AidData y GuySuCo.</t>
+        </is>
+      </c>
+      <c r="BC66" t="n">
         <v>0</v>
       </c>
-      <c r="BC66" t="inlineStr">
+      <c r="BD66" t="inlineStr"/>
+      <c r="BE66" t="inlineStr">
         <is>
           <t>https://china.aiddata.org/projects/55943/</t>
         </is>
       </c>
-      <c r="BD66" t="inlineStr">
+      <c r="BF66" t="inlineStr">
         <is>
           <t>https://guysuco.gy/index.php?option=com_k2&amp;view=item&amp;id=9:skeldon-sugar-modernisation-project-ssmp&amp;Itemid=277&amp;lang=en</t>
         </is>
       </c>
-      <c r="BE66" t="inlineStr">
+      <c r="BG66" t="inlineStr">
         <is>
           <t>https://www.stabroeknews.com/2023/11/18/opinion/editorial/revisionism-and-the-skeldon-sugar-factory/</t>
         </is>
       </c>
+      <c r="BH66" t="inlineStr"/>
+      <c r="BI66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9006,10 +11069,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G67" t="n">
+        <v>328</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -9060,6 +11121,9 @@
       <c r="R67" t="n">
         <v>28</v>
       </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -9075,22 +11139,59 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
+      <c r="AP67" t="inlineStr"/>
+      <c r="AQ67" t="inlineStr"/>
+      <c r="AR67" t="inlineStr"/>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AU67" t="inlineStr"/>
+      <c r="AV67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr"/>
+      <c r="AX67" t="inlineStr"/>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr"/>
       <c r="BA67" t="n">
         <v>3</v>
       </c>
-      <c r="BB67" t="n">
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>Fuentes confirman que CNQC (Qing Jian Group) participa en la construccion del nuevo cuartel general de la Policia de Guyana (Brickdam Police Station) por USD 28M, junto con R. Bassoo and Sons. La obra inicio en enero de 2024; la entrada registra el ano como 2025, pero el inicio del proyecto fue en 2024.</t>
+        </is>
+      </c>
+      <c r="BC67" t="n">
         <v>0</v>
       </c>
-      <c r="BC67" t="inlineStr">
+      <c r="BD67" t="inlineStr"/>
+      <c r="BE67" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2024/01/09/sod-turned-for-us28m-brickdam-police-station/</t>
         </is>
       </c>
-      <c r="BD67" t="inlineStr">
+      <c r="BF67" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2025/09/18/us28m-brickdam-police-station-on-track-for-june-2026-deadline/</t>
         </is>
       </c>
+      <c r="BG67" t="inlineStr"/>
+      <c r="BH67" t="inlineStr"/>
+      <c r="BI67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9119,10 +11220,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G68" t="n">
+        <v>328</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -9173,6 +11272,9 @@
       <c r="R68" t="n">
         <v>60</v>
       </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr">
         <is>
           <t>Adquisición</t>
@@ -9208,27 +11310,59 @@
           <t>http://ogneupor-spb.ru/besplatno/2.pdf</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
+      <c r="AP68" t="inlineStr"/>
+      <c r="AQ68" t="inlineStr"/>
+      <c r="AR68" t="inlineStr"/>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AU68" t="inlineStr"/>
+      <c r="AV68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr"/>
+      <c r="AX68" t="inlineStr"/>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
         <v>4</v>
       </c>
-      <c r="BB68" t="n">
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>Bien documentado: Bosai Minerals adquirió Omai Bauxite Mining Inc. de IAMGOLD a fines de 2006 por USD 46M (una fuente indica USD 60M inversión total). El monto registrado de USD 60M corresponde a la inversión total incluyendo capital de trabajo inicial. Confirmado por South China Morning Post, Globe and Mail y sitio oficial de Bosai.</t>
+        </is>
+      </c>
+      <c r="BC68" t="n">
         <v>0</v>
       </c>
-      <c r="BC68" t="inlineStr">
+      <c r="BD68" t="inlineStr"/>
+      <c r="BE68" t="inlineStr">
         <is>
           <t>https://www.scmp.com/article/579301/bosai-wins-bidding-guyana-bauxite-mines</t>
         </is>
       </c>
-      <c r="BD68" t="inlineStr">
+      <c r="BF68" t="inlineStr">
         <is>
           <t>https://www.theglobeandmail.com/report-on-business/iamgold-sells-stake-in-omai-bauxite-mining/article1111859/</t>
         </is>
       </c>
-      <c r="BE68" t="inlineStr">
+      <c r="BG68" t="inlineStr">
         <is>
           <t>https://en.cqbosai.com/about/fzlc/</t>
         </is>
       </c>
+      <c r="BH68" t="inlineStr"/>
+      <c r="BI68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9236,6 +11370,7 @@
           <t>GUY-0002</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
         <v>2</v>
       </c>
@@ -9254,10 +11389,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G69" t="n">
+        <v>328</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -9308,6 +11441,9 @@
       <c r="R69" t="n">
         <v>100</v>
       </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -9323,22 +11459,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
+      <c r="AP69" t="inlineStr"/>
+      <c r="AQ69" t="inlineStr"/>
+      <c r="AR69" t="inlineStr"/>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AU69" t="inlineStr"/>
+      <c r="AV69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr"/>
+      <c r="AX69" t="inlineStr"/>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr"/>
       <c r="BA69" t="n">
         <v>3</v>
       </c>
-      <c r="BB69" t="n">
+      <c r="BB69" t="inlineStr"/>
+      <c r="BC69" t="n">
         <v>0</v>
       </c>
-      <c r="BC69" t="inlineStr">
+      <c r="BD69" t="inlineStr"/>
+      <c r="BE69" t="inlineStr">
         <is>
           <t>https://latinoamerica21.com/en/china-expands-its-presence-in-guyana/</t>
         </is>
       </c>
-      <c r="BD69" t="inlineStr">
+      <c r="BF69" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2026/05/08/guyana-n0-3-in-global-rankings-for-chinese-investment/</t>
         </is>
       </c>
+      <c r="BG69" t="inlineStr"/>
+      <c r="BH69" t="inlineStr"/>
+      <c r="BI69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9346,6 +11515,7 @@
           <t>GUY-0020</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
         <v>20</v>
       </c>
@@ -9364,10 +11534,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G70" t="n">
+        <v>328</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -9418,6 +11586,9 @@
       <c r="R70" t="n">
         <v>236</v>
       </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -9433,22 +11604,55 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr"/>
+      <c r="AP70" t="inlineStr"/>
+      <c r="AQ70" t="inlineStr"/>
+      <c r="AR70" t="inlineStr"/>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AU70" t="inlineStr"/>
+      <c r="AV70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr"/>
+      <c r="AX70" t="inlineStr"/>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
         <v>3</v>
       </c>
-      <c r="BB70" t="n">
+      <c r="BB70" t="inlineStr"/>
+      <c r="BC70" t="n">
         <v>0</v>
       </c>
-      <c r="BC70" t="inlineStr">
+      <c r="BD70" t="inlineStr"/>
+      <c r="BE70" t="inlineStr">
         <is>
           <t>https://latinoamerica21.com/en/china-expands-its-presence-in-guyana/</t>
         </is>
       </c>
-      <c r="BD70" t="inlineStr">
+      <c r="BF70" t="inlineStr">
         <is>
           <t>https://kaieteurnewsonline.com/2026/05/08/guyana-n0-3-in-global-rankings-for-chinese-investment/</t>
         </is>
       </c>
+      <c r="BG70" t="inlineStr"/>
+      <c r="BH70" t="inlineStr"/>
+      <c r="BI70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9456,6 +11660,7 @@
           <t>GUY-0020</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
         <v>20</v>
       </c>
@@ -9474,10 +11679,8 @@
           <t>GUY</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
+      <c r="G71" t="n">
+        <v>328</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -9528,6 +11731,9 @@
       <c r="R71" t="n">
         <v>236</v>
       </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -9543,22 +11749,357 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
+      <c r="AP71" t="inlineStr"/>
+      <c r="AQ71" t="inlineStr"/>
+      <c r="AR71" t="inlineStr"/>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AU71" t="inlineStr"/>
+      <c r="AV71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr"/>
+      <c r="AX71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
         <v>3</v>
       </c>
-      <c r="BB71" t="n">
+      <c r="BB71" t="inlineStr"/>
+      <c r="BC71" t="n">
         <v>0</v>
       </c>
-      <c r="BC71" t="inlineStr">
+      <c r="BD71" t="inlineStr"/>
+      <c r="BE71" t="inlineStr">
         <is>
           <t>https://nationalinterest.org/blog/energy-world/suriname-china-and-the-new-cold-war</t>
         </is>
       </c>
-      <c r="BD71" t="inlineStr">
+      <c r="BF71" t="inlineStr">
         <is>
           <t>https://worldoil.com/magazine/2026/july/features/guyana-suriname-the-new-petro-state-corridor-takes-hold/</t>
         </is>
       </c>
+      <c r="BG71" t="inlineStr"/>
+      <c r="BH71" t="inlineStr"/>
+      <c r="BI71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>GUY-0021</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="n">
+        <v>21</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>5.950000, -57.150000</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>GUY</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>328</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>GY-EB</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>2026</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>China Road and Bridge Corporation</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Punto</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Construcción del puente sobre el río Corentyne</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Construction of the Corentyne river bridge</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Rio Corentyne, frontera Guyana-Surinam</t>
+        </is>
+      </c>
+      <c r="R72" t="n">
+        <v>236</v>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
+      <c r="AP72" t="inlineStr"/>
+      <c r="AQ72" t="inlineStr"/>
+      <c r="AR72" t="inlineStr"/>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AU72" t="inlineStr"/>
+      <c r="AV72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr"/>
+      <c r="AX72" t="inlineStr"/>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr"/>
+      <c r="BA72" t="inlineStr"/>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>Inversion aportada por Claire Espinosa y Allison Stronach, entrega del 20 de agosto de 2026. | Proyecto conjunto con Surinam en la frontera del rio Corentyne (nota de Allison). Registrado en Guyana; si el equipo prefiere, puede duplicarse en Surinam. | SIN PUNTAJE DE FIABILIDAD: Claire y Allison lo dejaron a proposito para que lo asigne un revisor externo.</t>
+        </is>
+      </c>
+      <c r="BC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD72" t="inlineStr"/>
+      <c r="BE72" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2024/12/10/chinese-firm-wins-bid-to-build-corentyne-river-bridge/</t>
+        </is>
+      </c>
+      <c r="BF72" t="inlineStr">
+        <is>
+          <t>https://kaieteurnewsonline.com/2025/10/19/guyana-suriname-still-to-finalise-financing-for-corentyne-river-bridge-project/</t>
+        </is>
+      </c>
+      <c r="BG72" t="inlineStr">
+        <is>
+          <t>https://www.ctol.digital/news/guyana-suriname-china-bridge-corentyne-river-deal/</t>
+        </is>
+      </c>
+      <c r="BH72" t="inlineStr"/>
+      <c r="BI72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>GUY-0022</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="n">
+        <v>22</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>6.000000, -58.300000</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>GUY</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>328</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>GY-UD</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>SUMEC and XJ Group</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Punto</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Construcción del parque solar GUYSOL</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Construction of the GUYSOL solar park</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Linden, Alto Demerara-Berbice</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Construcción</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="inlineStr"/>
+      <c r="AQ73" t="inlineStr"/>
+      <c r="AR73" t="inlineStr"/>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AU73" t="inlineStr"/>
+      <c r="AV73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr"/>
+      <c r="AX73" t="inlineStr"/>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr"/>
+      <c r="BA73" t="inlineStr"/>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>Inversion aportada por Claire Espinosa y Allison Stronach, entrega del 20 de agosto de 2026. | SIN PUNTAJE DE FIABILIDAD: Claire y Allison lo dejaron a proposito para que lo asigne un revisor externo. | Consorcio SUMEC Complete Equipment &amp; Engineering con XJ Group Corporation, escrito segun la convencion de consorcios de la base.</t>
+        </is>
+      </c>
+      <c r="BC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD73" t="inlineStr"/>
+      <c r="BE73" t="inlineStr">
+        <is>
+          <t>https://www.pv-magazine.com/2026/01/21/guyana-plans-three-utility-scale-solar-parks/</t>
+        </is>
+      </c>
+      <c r="BF73" t="inlineStr">
+        <is>
+          <t>https://guyanachronicle.com/2026/01/20/linden-poised-for-major-power-relief-as-govt-rolls-out-guysol-solar-project/</t>
+        </is>
+      </c>
+      <c r="BG73" t="inlineStr">
+        <is>
+          <t>https://renewablesnow.com/news/chinas-sumec-signs-contract-to-build-18-mw-of-solar-in-guyana-853109/</t>
+        </is>
+      </c>
+      <c r="BH73" t="inlineStr"/>
+      <c r="BI73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/sources/countries/guyana.xlsx
+++ b/data/sources/countries/guyana.xlsx
@@ -7782,12 +7782,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Construcción De Plantas De Tratamiento De Agua En Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor, East Canje, And Berbice</t>
+          <t>Construcción De Plantas De Tratamiento De Agua En Uitvlugt, West Coast Demerara, Diamond, East Bank,</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Construction Of Water Treatment Plants At Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor, East Canje, And Berbice</t>
+          <t>Construction Of Water Treatment Plants At Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor,</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -7941,12 +7941,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Construcción De Plantas De Tratamiento De Agua En Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor, East Canje, And Berbice</t>
+          <t>Construcción De Plantas De Tratamiento De Agua En Uitvlugt, West Coast Demerara, Diamond, East Bank,</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Construction Of Water Treatment Plants At Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor, East Canje, And Berbice</t>
+          <t>Construction Of Water Treatment Plants At Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor,</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Construcción De Plantas De Tratamiento De Agua En Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor, East Canje, And Berbice</t>
+          <t>Construcción De Plantas De Tratamiento De Agua En Uitvlugt, West Coast Demerara, Diamond, East Bank,</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Construction Of Water Treatment Plants At Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor, East Canje, And Berbice</t>
+          <t>Construction Of Water Treatment Plants At Uitvlugt, West Coast Demerara, Diamond, East Bank, Demerara And Sheet Anchor,</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Expansion of the former Pegasus Hotel in Georgetown into the Pegasus Suites and Corporate Centre. CHEC was the contractor; the owner is Guyanese investor Robert Badal, so this is not Chinese FDI.</t>
+          <t>Expansion of the former Pegasus Hotel in Georgetown into the Pegasus Suites and Corporate Centre.</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
